--- a/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_60_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_60_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_60_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_60_10_test.xlsx
@@ -510,7 +510,7 @@
         <v>-6568.865924444445</v>
       </c>
       <c r="G3" t="n">
-        <v>-6580.427438090119</v>
+        <v>-6580.42743809012</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>-6630.279941296297</v>
       </c>
       <c r="G7" t="n">
-        <v>-6645.106241867861</v>
+        <v>-6645.10624186786</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         <v>-6670.232917037037</v>
       </c>
       <c r="G9" t="n">
-        <v>-6688.457644735989</v>
+        <v>-6688.457644735988</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
         <v>-6560.624371481482</v>
       </c>
       <c r="G12" t="n">
-        <v>-6583.926106168308</v>
+        <v>-6583.92610616831</v>
       </c>
     </row>
     <row r="13">
@@ -779,13 +779,13 @@
         <v>-362.22148763</v>
       </c>
       <c r="E14" t="n">
-        <v>-363.3725971572397</v>
+        <v>-363.3725971572398</v>
       </c>
       <c r="F14" t="n">
         <v>-6707.805326481482</v>
       </c>
       <c r="G14" t="n">
-        <v>-6729.122169578513</v>
+        <v>-6729.122169578514</v>
       </c>
     </row>
     <row r="15">
@@ -829,13 +829,13 @@
         <v>-357.2238307</v>
       </c>
       <c r="E16" t="n">
-        <v>-357.971970977048</v>
+        <v>-357.9719709770481</v>
       </c>
       <c r="F16" t="n">
         <v>-6615.256124074074</v>
       </c>
       <c r="G16" t="n">
-        <v>-6629.110573649038</v>
+        <v>-6629.110573649039</v>
       </c>
     </row>
     <row r="17">
@@ -904,13 +904,13 @@
         <v>-362.05891302</v>
       </c>
       <c r="E19" t="n">
-        <v>-362.6376112068126</v>
+        <v>-362.6376112068125</v>
       </c>
       <c r="F19" t="n">
         <v>-6704.794685555556</v>
       </c>
       <c r="G19" t="n">
-        <v>-6715.511318644678</v>
+        <v>-6715.511318644676</v>
       </c>
     </row>
     <row r="20">
@@ -1004,13 +1004,13 @@
         <v>-357.8744833</v>
       </c>
       <c r="E23" t="n">
-        <v>-358.3677330543151</v>
+        <v>-358.367733054315</v>
       </c>
       <c r="F23" t="n">
         <v>-6627.305246296297</v>
       </c>
       <c r="G23" t="n">
-        <v>-6636.439501005835</v>
+        <v>-6636.439501005832</v>
       </c>
     </row>
     <row r="24">
@@ -1035,7 +1035,7 @@
         <v>-6654.565425740741</v>
       </c>
       <c r="G24" t="n">
-        <v>-6670.532804268408</v>
+        <v>-6670.532804268407</v>
       </c>
     </row>
     <row r="25">
@@ -1054,13 +1054,13 @@
         <v>-357.66477533</v>
       </c>
       <c r="E25" t="n">
-        <v>-358.3709712304256</v>
+        <v>-358.3709712304257</v>
       </c>
       <c r="F25" t="n">
         <v>-6623.42176537037</v>
       </c>
       <c r="G25" t="n">
-        <v>-6636.499467230104</v>
+        <v>-6636.499467230105</v>
       </c>
     </row>
     <row r="26">
@@ -1104,13 +1104,13 @@
         <v>-356.21036234</v>
       </c>
       <c r="E27" t="n">
-        <v>-357.0347829357396</v>
+        <v>-357.0347829357395</v>
       </c>
       <c r="F27" t="n">
         <v>-6596.488191481481</v>
       </c>
       <c r="G27" t="n">
-        <v>-6611.755239550734</v>
+        <v>-6611.755239550733</v>
       </c>
     </row>
     <row r="28">
@@ -1129,13 +1129,13 @@
         <v>-356.21541885</v>
       </c>
       <c r="E28" t="n">
-        <v>-357.0534413561265</v>
+        <v>-357.0534413561264</v>
       </c>
       <c r="F28" t="n">
         <v>-6596.581830555556</v>
       </c>
       <c r="G28" t="n">
-        <v>-6612.100765854195</v>
+        <v>-6612.100765854194</v>
       </c>
     </row>
     <row r="29">
@@ -1185,7 +1185,7 @@
         <v>-6635.867902222223</v>
       </c>
       <c r="G30" t="n">
-        <v>-6561.620900303864</v>
+        <v>-6561.620900303862</v>
       </c>
     </row>
     <row r="31">
@@ -1229,13 +1229,13 @@
         <v>-355.47898358</v>
       </c>
       <c r="E32" t="n">
-        <v>-356.7297589047516</v>
+        <v>-356.7297589047515</v>
       </c>
       <c r="F32" t="n">
         <v>-6582.94414037037</v>
       </c>
       <c r="G32" t="n">
-        <v>-6606.106646384288</v>
+        <v>-6606.106646384287</v>
       </c>
     </row>
     <row r="33">
@@ -1279,13 +1279,13 @@
         <v>-356.45427226</v>
       </c>
       <c r="E34" t="n">
-        <v>-357.3519298159209</v>
+        <v>-357.3519298159208</v>
       </c>
       <c r="F34" t="n">
         <v>-6601.005041851852</v>
       </c>
       <c r="G34" t="n">
-        <v>-6617.628329924461</v>
+        <v>-6617.62832992446</v>
       </c>
     </row>
     <row r="35">
@@ -1504,13 +1504,13 @@
         <v>-357.31906232</v>
       </c>
       <c r="E43" t="n">
-        <v>-358.279963037402</v>
+        <v>-358.2799630374021</v>
       </c>
       <c r="F43" t="n">
         <v>-6617.019672592593</v>
       </c>
       <c r="G43" t="n">
-        <v>-6634.814130322259</v>
+        <v>-6634.814130322262</v>
       </c>
     </row>
     <row r="44">
@@ -1610,7 +1610,7 @@
         <v>-6662.989622592593</v>
       </c>
       <c r="G47" t="n">
-        <v>-6680.186767897732</v>
+        <v>-6680.186767897731</v>
       </c>
     </row>
     <row r="48">
@@ -1679,13 +1679,13 @@
         <v>-360.93669237</v>
       </c>
       <c r="E50" t="n">
-        <v>-361.7704432477277</v>
+        <v>-361.7704432477276</v>
       </c>
       <c r="F50" t="n">
         <v>-6684.012821666667</v>
       </c>
       <c r="G50" t="n">
-        <v>-6699.452652735697</v>
+        <v>-6699.452652735696</v>
       </c>
     </row>
     <row r="51">
@@ -1779,13 +1779,13 @@
         <v>-351.98155875</v>
       </c>
       <c r="E54" t="n">
-        <v>-353.107369894617</v>
+        <v>-353.1073698946171</v>
       </c>
       <c r="F54" t="n">
         <v>-6518.177013888889</v>
       </c>
       <c r="G54" t="n">
-        <v>-6539.025368418834</v>
+        <v>-6539.025368418835</v>
       </c>
     </row>
     <row r="55">
@@ -1810,7 +1810,7 @@
         <v>-6670.979818333333</v>
       </c>
       <c r="G55" t="n">
-        <v>-6601.695527544162</v>
+        <v>-6601.695527544161</v>
       </c>
     </row>
     <row r="56">
@@ -1879,13 +1879,13 @@
         <v>-357.05933372</v>
       </c>
       <c r="E58" t="n">
-        <v>-357.6206227468645</v>
+        <v>-357.6206227468644</v>
       </c>
       <c r="F58" t="n">
         <v>-6612.209883703704</v>
       </c>
       <c r="G58" t="n">
-        <v>-6622.604124941934</v>
+        <v>-6622.604124941933</v>
       </c>
     </row>
     <row r="59">
@@ -1954,13 +1954,13 @@
         <v>-360.61631043</v>
       </c>
       <c r="E61" t="n">
-        <v>-361.3854457070981</v>
+        <v>-361.3854457070983</v>
       </c>
       <c r="F61" t="n">
         <v>-6678.079822777778</v>
       </c>
       <c r="G61" t="n">
-        <v>-6692.323068649966</v>
+        <v>-6692.323068649967</v>
       </c>
     </row>
     <row r="62">
@@ -2035,7 +2035,7 @@
         <v>-6658.844139074075</v>
       </c>
       <c r="G64" t="n">
-        <v>-6670.822693667456</v>
+        <v>-6670.822693667457</v>
       </c>
     </row>
     <row r="65">
@@ -2054,7 +2054,7 @@
         <v>-120.42308565</v>
       </c>
       <c r="E65" t="n">
-        <v>-118.9389418013115</v>
+        <v>-118.9389418013114</v>
       </c>
       <c r="F65" t="n">
         <v>-6690.171425</v>
@@ -2079,13 +2079,13 @@
         <v>-119.7747379</v>
       </c>
       <c r="E66" t="n">
-        <v>-118.4729924611844</v>
+        <v>-118.4729924611843</v>
       </c>
       <c r="F66" t="n">
         <v>-6654.152105555556</v>
       </c>
       <c r="G66" t="n">
-        <v>-6581.832914510243</v>
+        <v>-6581.832914510241</v>
       </c>
     </row>
     <row r="67">
@@ -2254,7 +2254,7 @@
         <v>-350.51577832</v>
       </c>
       <c r="E73" t="n">
-        <v>-351.0386162499942</v>
+        <v>-351.0386162499941</v>
       </c>
       <c r="F73" t="n">
         <v>-6491.032931851852</v>
@@ -2304,13 +2304,13 @@
         <v>-359.85594239</v>
       </c>
       <c r="E75" t="n">
-        <v>-360.3189430170759</v>
+        <v>-360.3189430170758</v>
       </c>
       <c r="F75" t="n">
         <v>-6663.998933148147</v>
       </c>
       <c r="G75" t="n">
-        <v>-6672.573018834739</v>
+        <v>-6672.573018834738</v>
       </c>
     </row>
     <row r="76">
@@ -2385,7 +2385,7 @@
         <v>-6630.712915740741</v>
       </c>
       <c r="G78" t="n">
-        <v>-6650.028322476582</v>
+        <v>-6650.028322476581</v>
       </c>
     </row>
     <row r="79">
@@ -2454,13 +2454,13 @@
         <v>-356.91773061</v>
       </c>
       <c r="E81" t="n">
-        <v>-357.5699279137028</v>
+        <v>-357.5699279137027</v>
       </c>
       <c r="F81" t="n">
         <v>-6609.587603888888</v>
       </c>
       <c r="G81" t="n">
-        <v>-6621.665331735237</v>
+        <v>-6621.665331735236</v>
       </c>
     </row>
     <row r="82">
@@ -2635,7 +2635,7 @@
         <v>-6685.642029629629</v>
       </c>
       <c r="G88" t="n">
-        <v>-6697.815400043522</v>
+        <v>-6697.815400043521</v>
       </c>
     </row>
     <row r="89">
@@ -2660,7 +2660,7 @@
         <v>-6639.325515555556</v>
       </c>
       <c r="G89" t="n">
-        <v>-6562.298567165505</v>
+        <v>-6562.298567165503</v>
       </c>
     </row>
     <row r="90">
@@ -2710,7 +2710,7 @@
         <v>-6453.846223333333</v>
       </c>
       <c r="G91" t="n">
-        <v>-6470.843913706768</v>
+        <v>-6470.843913706766</v>
       </c>
     </row>
     <row r="92">
@@ -2760,7 +2760,7 @@
         <v>-6612.370690555555</v>
       </c>
       <c r="G93" t="n">
-        <v>-6528.826055151195</v>
+        <v>-6528.826055151193</v>
       </c>
     </row>
     <row r="94">
@@ -2829,13 +2829,13 @@
         <v>-361.15611498</v>
       </c>
       <c r="E96" t="n">
-        <v>-361.8431576004558</v>
+        <v>-361.8431576004559</v>
       </c>
       <c r="F96" t="n">
         <v>-6688.076203333332</v>
       </c>
       <c r="G96" t="n">
-        <v>-6700.799214823255</v>
+        <v>-6700.799214823258</v>
       </c>
     </row>
     <row r="97">
@@ -2854,13 +2854,13 @@
         <v>-361.53601897</v>
       </c>
       <c r="E97" t="n">
-        <v>-362.1667199509586</v>
+        <v>-362.1667199509585</v>
       </c>
       <c r="F97" t="n">
         <v>-6695.111462407407</v>
       </c>
       <c r="G97" t="n">
-        <v>-6706.791110202937</v>
+        <v>-6706.791110202936</v>
       </c>
     </row>
     <row r="98">
@@ -2904,13 +2904,13 @@
         <v>-346.29628625</v>
       </c>
       <c r="E99" t="n">
-        <v>-346.9117927161715</v>
+        <v>-346.9117927161714</v>
       </c>
       <c r="F99" t="n">
         <v>-6412.894189814815</v>
       </c>
       <c r="G99" t="n">
-        <v>-6424.292457706879</v>
+        <v>-6424.292457706878</v>
       </c>
     </row>
     <row r="100">
@@ -3079,13 +3079,13 @@
         <v>-360.11768403</v>
       </c>
       <c r="E106" t="n">
-        <v>-360.7999479159394</v>
+        <v>-360.7999479159393</v>
       </c>
       <c r="F106" t="n">
         <v>-6668.846000555555</v>
       </c>
       <c r="G106" t="n">
-        <v>-6681.48051696184</v>
+        <v>-6681.480516961839</v>
       </c>
     </row>
     <row r="107">
@@ -3110,7 +3110,7 @@
         <v>-6683.170386296297</v>
       </c>
       <c r="G107" t="n">
-        <v>-6698.053737959084</v>
+        <v>-6698.053737959083</v>
       </c>
     </row>
     <row r="108">
@@ -3179,13 +3179,13 @@
         <v>-362.33257344</v>
       </c>
       <c r="E110" t="n">
-        <v>-362.9287462612346</v>
+        <v>-362.9287462612345</v>
       </c>
       <c r="F110" t="n">
         <v>-6709.862471111111</v>
       </c>
       <c r="G110" t="n">
-        <v>-6720.902708541381</v>
+        <v>-6720.90270854138</v>
       </c>
     </row>
     <row r="111">
@@ -3229,13 +3229,13 @@
         <v>-357.37943906</v>
       </c>
       <c r="E112" t="n">
-        <v>-358.2097373094377</v>
+        <v>-358.2097373094379</v>
       </c>
       <c r="F112" t="n">
         <v>-6618.13776037037</v>
       </c>
       <c r="G112" t="n">
-        <v>-6633.513653878477</v>
+        <v>-6633.513653878478</v>
       </c>
     </row>
     <row r="113">
@@ -3254,13 +3254,13 @@
         <v>-362.0137009</v>
       </c>
       <c r="E113" t="n">
-        <v>-362.5810099161143</v>
+        <v>-362.5810099161142</v>
       </c>
       <c r="F113" t="n">
         <v>-6703.957424074074</v>
       </c>
       <c r="G113" t="n">
-        <v>-6714.463146594709</v>
+        <v>-6714.463146594708</v>
       </c>
     </row>
     <row r="114">
@@ -3285,7 +3285,7 @@
         <v>-6463.894317777777</v>
       </c>
       <c r="G114" t="n">
-        <v>-6401.543070414727</v>
+        <v>-6401.543070414726</v>
       </c>
     </row>
     <row r="115">
@@ -3335,7 +3335,7 @@
         <v>-6663.408522037037</v>
       </c>
       <c r="G116" t="n">
-        <v>-6675.738752697571</v>
+        <v>-6675.73875269757</v>
       </c>
     </row>
     <row r="117">
@@ -3360,7 +3360,7 @@
         <v>-6657.02001462963</v>
       </c>
       <c r="G117" t="n">
-        <v>-6675.641917133162</v>
+        <v>-6675.641917133161</v>
       </c>
     </row>
     <row r="118">
@@ -3454,13 +3454,13 @@
         <v>-357.45867594</v>
       </c>
       <c r="E121" t="n">
-        <v>-358.2282558632154</v>
+        <v>-358.2282558632153</v>
       </c>
       <c r="F121" t="n">
         <v>-6619.60511</v>
       </c>
       <c r="G121" t="n">
-        <v>-6633.856590059544</v>
+        <v>-6633.856590059543</v>
       </c>
     </row>
     <row r="122">
@@ -3535,7 +3535,7 @@
         <v>-6842.795679444444</v>
       </c>
       <c r="G124" t="n">
-        <v>-6762.940956521566</v>
+        <v>-6762.940956521565</v>
       </c>
     </row>
     <row r="125">
@@ -3660,7 +3660,7 @@
         <v>-6731.819887222223</v>
       </c>
       <c r="G129" t="n">
-        <v>-6659.976537372779</v>
+        <v>-6659.976537372777</v>
       </c>
     </row>
     <row r="130">
@@ -3685,7 +3685,7 @@
         <v>-6798.320042222223</v>
       </c>
       <c r="G130" t="n">
-        <v>-6709.847617276479</v>
+        <v>-6709.847617276477</v>
       </c>
     </row>
     <row r="131">
@@ -3710,7 +3710,7 @@
         <v>-6717.499670000001</v>
       </c>
       <c r="G131" t="n">
-        <v>-6730.514738785731</v>
+        <v>-6730.51473878573</v>
       </c>
     </row>
     <row r="132">
@@ -3735,7 +3735,7 @@
         <v>-6724.165088333333</v>
       </c>
       <c r="G132" t="n">
-        <v>-6652.986608860573</v>
+        <v>-6652.986608860571</v>
       </c>
     </row>
     <row r="133">
@@ -3860,7 +3860,7 @@
         <v>-6768.684429999999</v>
       </c>
       <c r="G137" t="n">
-        <v>-6680.429469263745</v>
+        <v>-6680.429469263743</v>
       </c>
     </row>
     <row r="138">
@@ -3910,7 +3910,7 @@
         <v>-6807.817181111111</v>
       </c>
       <c r="G139" t="n">
-        <v>-6730.512793834834</v>
+        <v>-6730.512793834832</v>
       </c>
     </row>
     <row r="140">
@@ -3954,13 +3954,13 @@
         <v>-362.67717311</v>
       </c>
       <c r="E141" t="n">
-        <v>-363.4942258604575</v>
+        <v>-363.4942258604576</v>
       </c>
       <c r="F141" t="n">
         <v>-6716.243946481482</v>
       </c>
       <c r="G141" t="n">
-        <v>-6731.374552971435</v>
+        <v>-6731.374552971437</v>
       </c>
     </row>
     <row r="142">
@@ -4110,7 +4110,7 @@
         <v>-6781.524434444445</v>
       </c>
       <c r="G147" t="n">
-        <v>-6702.90688470643</v>
+        <v>-6702.906884706429</v>
       </c>
     </row>
     <row r="148">
@@ -4160,7 +4160,7 @@
         <v>-6731.414088703704</v>
       </c>
       <c r="G149" t="n">
-        <v>-6746.746233905439</v>
+        <v>-6746.746233905438</v>
       </c>
     </row>
     <row r="150">
@@ -4210,7 +4210,7 @@
         <v>-6723.580241666667</v>
       </c>
       <c r="G151" t="n">
-        <v>-6635.85977985184</v>
+        <v>-6635.859779851839</v>
       </c>
     </row>
     <row r="152">
@@ -4354,13 +4354,13 @@
         <v>-362.56642406</v>
       </c>
       <c r="E157" t="n">
-        <v>-363.4093146969449</v>
+        <v>-363.4093146969448</v>
       </c>
       <c r="F157" t="n">
         <v>-6714.193038148148</v>
       </c>
       <c r="G157" t="n">
-        <v>-6729.802124017498</v>
+        <v>-6729.802124017496</v>
       </c>
     </row>
     <row r="158">
@@ -4385,7 +4385,7 @@
         <v>-6763.803770925926</v>
       </c>
       <c r="G158" t="n">
-        <v>-6771.325808288692</v>
+        <v>-6771.325808288693</v>
       </c>
     </row>
     <row r="159">
@@ -4554,13 +4554,13 @@
         <v>-364.95483665</v>
       </c>
       <c r="E165" t="n">
-        <v>-365.8473092164986</v>
+        <v>-365.8473092164984</v>
       </c>
       <c r="F165" t="n">
         <v>-6758.422900925926</v>
       </c>
       <c r="G165" t="n">
-        <v>-6774.950170675899</v>
+        <v>-6774.950170675897</v>
       </c>
     </row>
     <row r="166">
@@ -4585,7 +4585,7 @@
         <v>-6857.430898888889</v>
       </c>
       <c r="G166" t="n">
-        <v>-6784.838928042061</v>
+        <v>-6784.838928042059</v>
       </c>
     </row>
     <row r="167">
@@ -4604,13 +4604,13 @@
         <v>-121.85071644</v>
       </c>
       <c r="E167" t="n">
-        <v>-120.464149190973</v>
+        <v>-120.4641491909729</v>
       </c>
       <c r="F167" t="n">
         <v>-6769.484246666667</v>
       </c>
       <c r="G167" t="n">
-        <v>-6692.452732831832</v>
+        <v>-6692.45273283183</v>
       </c>
     </row>
     <row r="168">
@@ -4654,7 +4654,7 @@
         <v>-364.73288873</v>
       </c>
       <c r="E169" t="n">
-        <v>-365.7556788260229</v>
+        <v>-365.7556788260228</v>
       </c>
       <c r="F169" t="n">
         <v>-6754.312754259259</v>
@@ -4810,7 +4810,7 @@
         <v>-6755.088472222222</v>
       </c>
       <c r="G175" t="n">
-        <v>-6676.440015020405</v>
+        <v>-6676.440015020406</v>
       </c>
     </row>
     <row r="176">
@@ -5010,7 +5010,7 @@
         <v>-7331.82710375</v>
       </c>
       <c r="G183" t="n">
-        <v>-7325.246905351374</v>
+        <v>-7325.246905351375</v>
       </c>
     </row>
     <row r="184">
@@ -5060,7 +5060,7 @@
         <v>-7433.674828124999</v>
       </c>
       <c r="G185" t="n">
-        <v>-7433.575919543636</v>
+        <v>-7433.575919543634</v>
       </c>
     </row>
     <row r="186">
@@ -5185,7 +5185,7 @@
         <v>-7985.12438375</v>
       </c>
       <c r="G190" t="n">
-        <v>-8011.157383545897</v>
+        <v>-8011.157383545895</v>
       </c>
     </row>
     <row r="191">
@@ -5285,7 +5285,7 @@
         <v>-8006.567358125</v>
       </c>
       <c r="G194" t="n">
-        <v>-8027.79035399198</v>
+        <v>-8027.790353991982</v>
       </c>
     </row>
     <row r="195">
@@ -5385,7 +5385,7 @@
         <v>-8107.058170625</v>
       </c>
       <c r="G198" t="n">
-        <v>-8126.836765669653</v>
+        <v>-8126.836765669651</v>
       </c>
     </row>
     <row r="199">
@@ -5435,7 +5435,7 @@
         <v>-7628.537033125001</v>
       </c>
       <c r="G200" t="n">
-        <v>-7626.094817835996</v>
+        <v>-7626.094817835995</v>
       </c>
     </row>
     <row r="201">
@@ -5460,7 +5460,7 @@
         <v>-7758.30833875</v>
       </c>
       <c r="G201" t="n">
-        <v>-7755.862682049465</v>
+        <v>-7755.862682049466</v>
       </c>
     </row>
     <row r="202">
@@ -5485,7 +5485,7 @@
         <v>-7669.8874375</v>
       </c>
       <c r="G202" t="n">
-        <v>-7666.924580296226</v>
+        <v>-7666.924580296225</v>
       </c>
     </row>
     <row r="203">
@@ -5625,13 +5625,13 @@
         <v>-355.76357702</v>
       </c>
       <c r="E2" t="n">
-        <v>-356.4502457175484</v>
+        <v>-356.4502457175483</v>
       </c>
       <c r="F2" t="n">
         <v>-6588.214389259259</v>
       </c>
       <c r="G2" t="n">
-        <v>-6600.930476250896</v>
+        <v>-6600.930476250895</v>
       </c>
     </row>
     <row r="3">
@@ -5700,13 +5700,13 @@
         <v>-362.11692484</v>
       </c>
       <c r="E5" t="n">
-        <v>-362.8627009406637</v>
+        <v>-362.8627009406636</v>
       </c>
       <c r="F5" t="n">
         <v>-6705.86897851852</v>
       </c>
       <c r="G5" t="n">
-        <v>-6719.679647049327</v>
+        <v>-6719.679647049326</v>
       </c>
     </row>
     <row r="6">
@@ -5725,13 +5725,13 @@
         <v>-356.93747034</v>
       </c>
       <c r="E6" t="n">
-        <v>-357.7965104828848</v>
+        <v>-357.7965104828847</v>
       </c>
       <c r="F6" t="n">
         <v>-6609.953154444444</v>
       </c>
       <c r="G6" t="n">
-        <v>-6625.861305238608</v>
+        <v>-6625.861305238607</v>
       </c>
     </row>
     <row r="7">
@@ -5800,13 +5800,13 @@
         <v>-120.59041626</v>
       </c>
       <c r="E9" t="n">
-        <v>-118.9634481153378</v>
+        <v>-118.9634481153377</v>
       </c>
       <c r="F9" t="n">
         <v>-6699.46757</v>
       </c>
       <c r="G9" t="n">
-        <v>-6609.080450852099</v>
+        <v>-6609.080450852097</v>
       </c>
     </row>
     <row r="10">
@@ -5825,13 +5825,13 @@
         <v>-355.0396538</v>
       </c>
       <c r="E10" t="n">
-        <v>-355.6240840043156</v>
+        <v>-355.6240840043157</v>
       </c>
       <c r="F10" t="n">
         <v>-6574.808403703703</v>
       </c>
       <c r="G10" t="n">
-        <v>-6585.631185265105</v>
+        <v>-6585.631185265106</v>
       </c>
     </row>
     <row r="11">
@@ -5956,7 +5956,7 @@
         <v>-6617.953422962963</v>
       </c>
       <c r="G15" t="n">
-        <v>-6635.057455446761</v>
+        <v>-6635.057455446762</v>
       </c>
     </row>
     <row r="16">
@@ -6006,7 +6006,7 @@
         <v>-6388.229109444444</v>
       </c>
       <c r="G17" t="n">
-        <v>-6397.670060262968</v>
+        <v>-6397.670060262969</v>
       </c>
     </row>
     <row r="18">
@@ -6056,7 +6056,7 @@
         <v>-6538.083111111111</v>
       </c>
       <c r="G19" t="n">
-        <v>-6551.742404872998</v>
+        <v>-6551.742404872999</v>
       </c>
     </row>
     <row r="20">
@@ -6075,13 +6075,13 @@
         <v>-351.08775295</v>
       </c>
       <c r="E20" t="n">
-        <v>-352.3879831947844</v>
+        <v>-352.3879831947845</v>
       </c>
       <c r="F20" t="n">
         <v>-6501.62505462963</v>
       </c>
       <c r="G20" t="n">
-        <v>-6525.703392496007</v>
+        <v>-6525.703392496008</v>
       </c>
     </row>
     <row r="21">
@@ -6156,7 +6156,7 @@
         <v>-6546.578189999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-6557.351645869611</v>
+        <v>-6557.35164586961</v>
       </c>
     </row>
     <row r="24">
@@ -6281,7 +6281,7 @@
         <v>-6591.717659814814</v>
       </c>
       <c r="G28" t="n">
-        <v>-6609.098523340838</v>
+        <v>-6609.098523340836</v>
       </c>
     </row>
     <row r="29">
@@ -6350,13 +6350,13 @@
         <v>-356.82895077</v>
       </c>
       <c r="E31" t="n">
-        <v>-357.8970007098479</v>
+        <v>-357.8970007098478</v>
       </c>
       <c r="F31" t="n">
         <v>-6607.943532777777</v>
       </c>
       <c r="G31" t="n">
-        <v>-6627.722235367553</v>
+        <v>-6627.722235367552</v>
       </c>
     </row>
     <row r="32">
@@ -6525,13 +6525,13 @@
         <v>-358.56298625</v>
       </c>
       <c r="E38" t="n">
-        <v>-359.3739407287524</v>
+        <v>-359.3739407287525</v>
       </c>
       <c r="F38" t="n">
         <v>-6640.055300925927</v>
       </c>
       <c r="G38" t="n">
-        <v>-6655.072976458377</v>
+        <v>-6655.072976458379</v>
       </c>
     </row>
     <row r="39">
@@ -6550,13 +6550,13 @@
         <v>-361.78066223</v>
       </c>
       <c r="E39" t="n">
-        <v>-362.5928338710775</v>
+        <v>-362.5928338710774</v>
       </c>
       <c r="F39" t="n">
         <v>-6699.641893148148</v>
       </c>
       <c r="G39" t="n">
-        <v>-6714.682108723658</v>
+        <v>-6714.682108723656</v>
       </c>
     </row>
     <row r="40">
@@ -6575,13 +6575,13 @@
         <v>-360.70362154</v>
       </c>
       <c r="E40" t="n">
-        <v>-362.0292279059765</v>
+        <v>-362.0292279059764</v>
       </c>
       <c r="F40" t="n">
         <v>-6679.696695185185</v>
       </c>
       <c r="G40" t="n">
-        <v>-6704.244961221786</v>
+        <v>-6704.244961221785</v>
       </c>
     </row>
     <row r="41">
@@ -6650,13 +6650,13 @@
         <v>-361.41421571</v>
       </c>
       <c r="E43" t="n">
-        <v>-362.3325017905055</v>
+        <v>-362.3325017905053</v>
       </c>
       <c r="F43" t="n">
         <v>-6692.855846481481</v>
       </c>
       <c r="G43" t="n">
-        <v>-6709.86114426862</v>
+        <v>-6709.861144268617</v>
       </c>
     </row>
     <row r="44">
@@ -6675,13 +6675,13 @@
         <v>-362.09463069</v>
       </c>
       <c r="E44" t="n">
-        <v>-362.9923838500965</v>
+        <v>-362.9923838500964</v>
       </c>
       <c r="F44" t="n">
         <v>-6705.456123888888</v>
       </c>
       <c r="G44" t="n">
-        <v>-6722.081182409194</v>
+        <v>-6722.081182409193</v>
       </c>
     </row>
     <row r="45">
@@ -6700,13 +6700,13 @@
         <v>-351.65762208</v>
       </c>
       <c r="E45" t="n">
-        <v>-352.5618613537075</v>
+        <v>-352.5618613537074</v>
       </c>
       <c r="F45" t="n">
         <v>-6512.178186666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-6528.923358401989</v>
+        <v>-6528.923358401988</v>
       </c>
     </row>
     <row r="46">
@@ -6750,13 +6750,13 @@
         <v>-354.80805708</v>
       </c>
       <c r="E47" t="n">
-        <v>-355.6062307144405</v>
+        <v>-355.6062307144404</v>
       </c>
       <c r="F47" t="n">
         <v>-6570.519575555555</v>
       </c>
       <c r="G47" t="n">
-        <v>-6585.300568785936</v>
+        <v>-6585.300568785933</v>
       </c>
     </row>
     <row r="48">
@@ -6775,13 +6775,13 @@
         <v>-352.76318022</v>
       </c>
       <c r="E48" t="n">
-        <v>-353.6209160672032</v>
+        <v>-353.6209160672033</v>
       </c>
       <c r="F48" t="n">
         <v>-6532.651485555555</v>
       </c>
       <c r="G48" t="n">
-        <v>-6548.535482725984</v>
+        <v>-6548.535482725986</v>
       </c>
     </row>
     <row r="49">
@@ -6800,7 +6800,7 @@
         <v>-356.29713668</v>
       </c>
       <c r="E49" t="n">
-        <v>-356.9306953009205</v>
+        <v>-356.9306953009204</v>
       </c>
       <c r="F49" t="n">
         <v>-6598.095123703703</v>
@@ -6831,7 +6831,7 @@
         <v>-6579.531924444444</v>
       </c>
       <c r="G50" t="n">
-        <v>-6591.086007980397</v>
+        <v>-6591.086007980396</v>
       </c>
     </row>
     <row r="51">
@@ -6850,13 +6850,13 @@
         <v>-361.00187758</v>
       </c>
       <c r="E51" t="n">
-        <v>-362.0478893712667</v>
+        <v>-362.0478893712666</v>
       </c>
       <c r="F51" t="n">
         <v>-6685.219955185185</v>
       </c>
       <c r="G51" t="n">
-        <v>-6704.590543912346</v>
+        <v>-6704.590543912345</v>
       </c>
     </row>
     <row r="52">
@@ -6900,13 +6900,13 @@
         <v>-360.86959674</v>
       </c>
       <c r="E53" t="n">
-        <v>-361.2408709067832</v>
+        <v>-361.2408709067831</v>
       </c>
       <c r="F53" t="n">
         <v>-6682.77031</v>
       </c>
       <c r="G53" t="n">
-        <v>-6689.645757533022</v>
+        <v>-6689.645757533021</v>
       </c>
     </row>
     <row r="54">
@@ -6931,7 +6931,7 @@
         <v>-6628.397512962963</v>
       </c>
       <c r="G54" t="n">
-        <v>-6647.491372106261</v>
+        <v>-6647.49137210626</v>
       </c>
     </row>
     <row r="55">
@@ -6950,7 +6950,7 @@
         <v>-358.5348658</v>
       </c>
       <c r="E55" t="n">
-        <v>-359.6290910841191</v>
+        <v>-359.629091084119</v>
       </c>
       <c r="F55" t="n">
         <v>-6639.534551851852</v>
@@ -6981,7 +6981,7 @@
         <v>-6520.350406111112</v>
       </c>
       <c r="G56" t="n">
-        <v>-6530.429908465082</v>
+        <v>-6530.429908465081</v>
       </c>
     </row>
     <row r="57">
@@ -7000,13 +7000,13 @@
         <v>-362.37033473</v>
       </c>
       <c r="E57" t="n">
-        <v>-363.0539910494066</v>
+        <v>-363.0539910494065</v>
       </c>
       <c r="F57" t="n">
         <v>-6710.561754259259</v>
       </c>
       <c r="G57" t="n">
-        <v>-6723.222056470492</v>
+        <v>-6723.22205647049</v>
       </c>
     </row>
     <row r="58">
@@ -7050,13 +7050,13 @@
         <v>-357.01213313</v>
       </c>
       <c r="E59" t="n">
-        <v>-357.8372674698194</v>
+        <v>-357.8372674698195</v>
       </c>
       <c r="F59" t="n">
         <v>-6611.335798703703</v>
       </c>
       <c r="G59" t="n">
-        <v>-6626.616064255916</v>
+        <v>-6626.616064255917</v>
       </c>
     </row>
     <row r="60">
@@ -7075,13 +7075,13 @@
         <v>-357.29565214</v>
       </c>
       <c r="E60" t="n">
-        <v>-358.0155791397987</v>
+        <v>-358.0155791397988</v>
       </c>
       <c r="F60" t="n">
         <v>-6616.586150740741</v>
       </c>
       <c r="G60" t="n">
-        <v>-6629.918132218495</v>
+        <v>-6629.918132218496</v>
       </c>
     </row>
     <row r="61">
@@ -7100,13 +7100,13 @@
         <v>-361.4085461</v>
       </c>
       <c r="E61" t="n">
-        <v>-361.8516737379393</v>
+        <v>-361.8516737379392</v>
       </c>
       <c r="F61" t="n">
         <v>-6692.750853703705</v>
       </c>
       <c r="G61" t="n">
-        <v>-6700.95692107295</v>
+        <v>-6700.956921072949</v>
       </c>
     </row>
     <row r="62">
@@ -7125,13 +7125,13 @@
         <v>-359.72982609</v>
       </c>
       <c r="E62" t="n">
-        <v>-360.1741977589133</v>
+        <v>-360.1741977589135</v>
       </c>
       <c r="F62" t="n">
         <v>-6661.663446111112</v>
       </c>
       <c r="G62" t="n">
-        <v>-6669.892551090987</v>
+        <v>-6669.892551090989</v>
       </c>
     </row>
     <row r="63">
@@ -7150,13 +7150,13 @@
         <v>-360.27798756</v>
       </c>
       <c r="E63" t="n">
-        <v>-361.259886878929</v>
+        <v>-361.2598868789289</v>
       </c>
       <c r="F63" t="n">
         <v>-6671.814584444444</v>
       </c>
       <c r="G63" t="n">
-        <v>-6689.997905165352</v>
+        <v>-6689.997905165351</v>
       </c>
     </row>
     <row r="64">
@@ -7175,13 +7175,13 @@
         <v>-356.92988655</v>
       </c>
       <c r="E64" t="n">
-        <v>-357.8835112594891</v>
+        <v>-357.8835112594892</v>
       </c>
       <c r="F64" t="n">
         <v>-6609.812713888889</v>
       </c>
       <c r="G64" t="n">
-        <v>-6627.47243073128</v>
+        <v>-6627.472430731281</v>
       </c>
     </row>
     <row r="65">
@@ -7225,13 +7225,13 @@
         <v>-357.28134034</v>
       </c>
       <c r="E66" t="n">
-        <v>-358.3784528023481</v>
+        <v>-358.3784528023479</v>
       </c>
       <c r="F66" t="n">
         <v>-6616.321117407408</v>
       </c>
       <c r="G66" t="n">
-        <v>-6636.638014858298</v>
+        <v>-6636.638014858294</v>
       </c>
     </row>
     <row r="67">
@@ -7250,13 +7250,13 @@
         <v>-360.60102876</v>
       </c>
       <c r="E67" t="n">
-        <v>-361.2890425848535</v>
+        <v>-361.2890425848537</v>
       </c>
       <c r="F67" t="n">
         <v>-6677.796828888889</v>
       </c>
       <c r="G67" t="n">
-        <v>-6690.537825645436</v>
+        <v>-6690.537825645439</v>
       </c>
     </row>
     <row r="68">
@@ -7281,7 +7281,7 @@
         <v>-6384.381257222222</v>
       </c>
       <c r="G68" t="n">
-        <v>-6291.31855363918</v>
+        <v>-6291.318553639179</v>
       </c>
     </row>
     <row r="69">
@@ -7350,13 +7350,13 @@
         <v>-120.17862857</v>
       </c>
       <c r="E71" t="n">
-        <v>-118.8720787137127</v>
+        <v>-118.8720787137126</v>
       </c>
       <c r="F71" t="n">
         <v>-6676.590476111111</v>
       </c>
       <c r="G71" t="n">
-        <v>-6604.004372984036</v>
+        <v>-6604.004372984035</v>
       </c>
     </row>
     <row r="72">
@@ -7400,13 +7400,13 @@
         <v>-345.68177126</v>
       </c>
       <c r="E73" t="n">
-        <v>-346.2227753544519</v>
+        <v>-346.2227753544518</v>
       </c>
       <c r="F73" t="n">
         <v>-6401.514282592593</v>
       </c>
       <c r="G73" t="n">
-        <v>-6411.532876934293</v>
+        <v>-6411.532876934292</v>
       </c>
     </row>
     <row r="74">
@@ -7431,7 +7431,7 @@
         <v>-6658.65745925926</v>
       </c>
       <c r="G74" t="n">
-        <v>-6672.103779578246</v>
+        <v>-6672.103779578248</v>
       </c>
     </row>
     <row r="75">
@@ -7456,7 +7456,7 @@
         <v>-6513.912111666667</v>
       </c>
       <c r="G75" t="n">
-        <v>-6534.664386776086</v>
+        <v>-6534.664386776085</v>
       </c>
     </row>
     <row r="76">
@@ -7475,13 +7475,13 @@
         <v>-116.22590605</v>
       </c>
       <c r="E76" t="n">
-        <v>-114.7284295303177</v>
+        <v>-114.7284295303176</v>
       </c>
       <c r="F76" t="n">
         <v>-6456.994780555556</v>
       </c>
       <c r="G76" t="n">
-        <v>-6373.801640573203</v>
+        <v>-6373.801640573202</v>
       </c>
     </row>
     <row r="77">
@@ -7500,13 +7500,13 @@
         <v>-120.31763289</v>
       </c>
       <c r="E77" t="n">
-        <v>-118.9761507448041</v>
+        <v>-118.9761507448042</v>
       </c>
       <c r="F77" t="n">
         <v>-6684.312938333333</v>
       </c>
       <c r="G77" t="n">
-        <v>-6609.786152489118</v>
+        <v>-6609.78615248912</v>
       </c>
     </row>
     <row r="78">
@@ -7525,13 +7525,13 @@
         <v>-358.43207124</v>
       </c>
       <c r="E78" t="n">
-        <v>-358.9545548453439</v>
+        <v>-358.954554845344</v>
       </c>
       <c r="F78" t="n">
         <v>-6637.630948888889</v>
       </c>
       <c r="G78" t="n">
-        <v>-6647.306571210072</v>
+        <v>-6647.306571210073</v>
       </c>
     </row>
     <row r="79">
@@ -7556,7 +7556,7 @@
         <v>-6663.874691481482</v>
       </c>
       <c r="G79" t="n">
-        <v>-6683.646733358422</v>
+        <v>-6683.646733358421</v>
       </c>
     </row>
     <row r="80">
@@ -7631,7 +7631,7 @@
         <v>-6488.593758333333</v>
       </c>
       <c r="G82" t="n">
-        <v>-6400.270540163641</v>
+        <v>-6400.270540163639</v>
       </c>
     </row>
     <row r="83">
@@ -7675,13 +7675,13 @@
         <v>-347.45164105</v>
       </c>
       <c r="E84" t="n">
-        <v>-348.0318084863527</v>
+        <v>-348.0318084863526</v>
       </c>
       <c r="F84" t="n">
         <v>-6434.289649074074</v>
       </c>
       <c r="G84" t="n">
-        <v>-6445.033490488013</v>
+        <v>-6445.033490488011</v>
       </c>
     </row>
     <row r="85">
@@ -7706,7 +7706,7 @@
         <v>-6547.531614629629</v>
       </c>
       <c r="G85" t="n">
-        <v>-6565.837768783089</v>
+        <v>-6565.837768783088</v>
       </c>
     </row>
     <row r="86">
@@ -7731,7 +7731,7 @@
         <v>-6661.633903148148</v>
       </c>
       <c r="G86" t="n">
-        <v>-6676.740231734664</v>
+        <v>-6676.740231734665</v>
       </c>
     </row>
     <row r="87">
@@ -7775,13 +7775,13 @@
         <v>-353.41656356</v>
       </c>
       <c r="E88" t="n">
-        <v>-354.2364508635374</v>
+        <v>-354.2364508635375</v>
       </c>
       <c r="F88" t="n">
         <v>-6544.751177037037</v>
       </c>
       <c r="G88" t="n">
-        <v>-6559.934275250694</v>
+        <v>-6559.934275250695</v>
       </c>
     </row>
     <row r="89">
@@ -7831,7 +7831,7 @@
         <v>-6618.03080925926</v>
       </c>
       <c r="G90" t="n">
-        <v>-6624.988495923144</v>
+        <v>-6624.988495923146</v>
       </c>
     </row>
     <row r="91">
@@ -7856,7 +7856,7 @@
         <v>-6351.866335000001</v>
       </c>
       <c r="G91" t="n">
-        <v>-6289.590672368442</v>
+        <v>-6289.59067236844</v>
       </c>
     </row>
     <row r="92">
@@ -7881,7 +7881,7 @@
         <v>-6566.855721296296</v>
       </c>
       <c r="G92" t="n">
-        <v>-6578.41244849019</v>
+        <v>-6578.412448490191</v>
       </c>
     </row>
     <row r="93">
@@ -7956,7 +7956,7 @@
         <v>-6576.761903333333</v>
       </c>
       <c r="G95" t="n">
-        <v>-6588.034414649494</v>
+        <v>-6588.034414649493</v>
       </c>
     </row>
     <row r="96">
@@ -7975,13 +7975,13 @@
         <v>-352.63138937</v>
       </c>
       <c r="E96" t="n">
-        <v>-353.6442535039502</v>
+        <v>-353.6442535039501</v>
       </c>
       <c r="F96" t="n">
         <v>-6530.21091425926</v>
       </c>
       <c r="G96" t="n">
-        <v>-6548.967657480558</v>
+        <v>-6548.967657480557</v>
       </c>
     </row>
     <row r="97">
@@ -8025,13 +8025,13 @@
         <v>-341.07639222</v>
       </c>
       <c r="E98" t="n">
-        <v>-342.0773986522957</v>
+        <v>-342.0773986522956</v>
       </c>
       <c r="F98" t="n">
         <v>-6316.229485555556</v>
       </c>
       <c r="G98" t="n">
-        <v>-6334.76664170918</v>
+        <v>-6334.766641709179</v>
       </c>
     </row>
     <row r="99">
@@ -8056,7 +8056,7 @@
         <v>-6574.568693703704</v>
       </c>
       <c r="G99" t="n">
-        <v>-6580.458760988775</v>
+        <v>-6580.458760988774</v>
       </c>
     </row>
     <row r="100">
@@ -8075,13 +8075,13 @@
         <v>-354.74344104</v>
       </c>
       <c r="E100" t="n">
-        <v>-355.4400202800977</v>
+        <v>-355.4400202800976</v>
       </c>
       <c r="F100" t="n">
         <v>-6569.322982222222</v>
       </c>
       <c r="G100" t="n">
-        <v>-6582.222597779586</v>
+        <v>-6582.222597779585</v>
       </c>
     </row>
     <row r="101">
@@ -8100,13 +8100,13 @@
         <v>-356.70641067</v>
       </c>
       <c r="E101" t="n">
-        <v>-357.1527301223461</v>
+        <v>-357.152730122346</v>
       </c>
       <c r="F101" t="n">
         <v>-6605.674271666667</v>
       </c>
       <c r="G101" t="n">
-        <v>-6613.939446710113</v>
+        <v>-6613.939446710112</v>
       </c>
     </row>
     <row r="102">
@@ -8125,13 +8125,13 @@
         <v>-360.11042278</v>
       </c>
       <c r="E102" t="n">
-        <v>-360.6166360039428</v>
+        <v>-360.6166360039427</v>
       </c>
       <c r="F102" t="n">
         <v>-6668.711532962963</v>
       </c>
       <c r="G102" t="n">
-        <v>-6678.085851924867</v>
+        <v>-6678.085851924866</v>
       </c>
     </row>
     <row r="103">
@@ -8181,7 +8181,7 @@
         <v>-6605.939077407408</v>
       </c>
       <c r="G104" t="n">
-        <v>-6629.322003223156</v>
+        <v>-6629.322003223155</v>
       </c>
     </row>
     <row r="105">
@@ -8231,7 +8231,7 @@
         <v>-6712.360348518519</v>
       </c>
       <c r="G106" t="n">
-        <v>-6722.794517249441</v>
+        <v>-6722.79451724944</v>
       </c>
     </row>
     <row r="107">
@@ -8281,7 +8281,7 @@
         <v>-6537.778917037037</v>
       </c>
       <c r="G108" t="n">
-        <v>-6557.62357479849</v>
+        <v>-6557.623574798489</v>
       </c>
     </row>
     <row r="109">
@@ -8300,13 +8300,13 @@
         <v>-357.87599347</v>
       </c>
       <c r="E109" t="n">
-        <v>-358.9704535430329</v>
+        <v>-358.970453543033</v>
       </c>
       <c r="F109" t="n">
         <v>-6627.333212407409</v>
       </c>
       <c r="G109" t="n">
-        <v>-6647.600991537647</v>
+        <v>-6647.600991537648</v>
       </c>
     </row>
     <row r="110">
@@ -8350,13 +8350,13 @@
         <v>-357.6263799</v>
       </c>
       <c r="E111" t="n">
-        <v>-358.3098375379589</v>
+        <v>-358.3098375379588</v>
       </c>
       <c r="F111" t="n">
         <v>-6622.710738888889</v>
       </c>
       <c r="G111" t="n">
-        <v>-6635.367361814053</v>
+        <v>-6635.367361814052</v>
       </c>
     </row>
     <row r="112">
@@ -8425,13 +8425,13 @@
         <v>-355.27252254</v>
       </c>
       <c r="E114" t="n">
-        <v>-355.5148163306927</v>
+        <v>-355.5148163306925</v>
       </c>
       <c r="F114" t="n">
         <v>-6579.120787777779</v>
       </c>
       <c r="G114" t="n">
-        <v>-6583.607709827642</v>
+        <v>-6583.607709827639</v>
       </c>
     </row>
     <row r="115">
@@ -8525,13 +8525,13 @@
         <v>-354.50484641</v>
       </c>
       <c r="E118" t="n">
-        <v>-355.0308728369011</v>
+        <v>-355.030872836901</v>
       </c>
       <c r="F118" t="n">
         <v>-6564.904563148149</v>
       </c>
       <c r="G118" t="n">
-        <v>-6574.645793275947</v>
+        <v>-6574.645793275945</v>
       </c>
     </row>
     <row r="119">
@@ -8600,13 +8600,13 @@
         <v>-360.94480644</v>
       </c>
       <c r="E121" t="n">
-        <v>-361.8122413316221</v>
+        <v>-361.812241331622</v>
       </c>
       <c r="F121" t="n">
         <v>-6684.163082222221</v>
       </c>
       <c r="G121" t="n">
-        <v>-6700.226691326335</v>
+        <v>-6700.226691326334</v>
       </c>
     </row>
     <row r="122">
@@ -8631,7 +8631,7 @@
         <v>-6543.381371481482</v>
       </c>
       <c r="G122" t="n">
-        <v>-6565.410944488593</v>
+        <v>-6565.410944488592</v>
       </c>
     </row>
     <row r="123">
@@ -8675,13 +8675,13 @@
         <v>-355.70500108</v>
       </c>
       <c r="E124" t="n">
-        <v>-356.8033054830093</v>
+        <v>-356.8033054830092</v>
       </c>
       <c r="F124" t="n">
         <v>-6587.12964962963</v>
       </c>
       <c r="G124" t="n">
-        <v>-6607.468620055728</v>
+        <v>-6607.468620055727</v>
       </c>
     </row>
     <row r="125">
@@ -8700,13 +8700,13 @@
         <v>-358.34213808</v>
       </c>
       <c r="E125" t="n">
-        <v>-359.2550840530321</v>
+        <v>-359.255084053032</v>
       </c>
       <c r="F125" t="n">
         <v>-6635.96552</v>
       </c>
       <c r="G125" t="n">
-        <v>-6652.871926908002</v>
+        <v>-6652.871926908001</v>
       </c>
     </row>
     <row r="126">
@@ -8725,13 +8725,13 @@
         <v>-353.92392061</v>
       </c>
       <c r="E126" t="n">
-        <v>-354.8335555157829</v>
+        <v>-354.8335555157828</v>
       </c>
       <c r="F126" t="n">
         <v>-6554.146677962963</v>
       </c>
       <c r="G126" t="n">
-        <v>-6570.991768810794</v>
+        <v>-6570.991768810793</v>
       </c>
     </row>
     <row r="127">
@@ -8806,7 +8806,7 @@
         <v>-6644.948775000001</v>
       </c>
       <c r="G129" t="n">
-        <v>-6668.082463700654</v>
+        <v>-6668.082463700653</v>
       </c>
     </row>
     <row r="130">
@@ -8831,7 +8831,7 @@
         <v>-6422.675071666667</v>
       </c>
       <c r="G130" t="n">
-        <v>-6437.234456184974</v>
+        <v>-6437.234456184973</v>
       </c>
     </row>
     <row r="131">
@@ -8850,13 +8850,13 @@
         <v>-346.60481576</v>
       </c>
       <c r="E131" t="n">
-        <v>-347.1789352450454</v>
+        <v>-347.1789352450453</v>
       </c>
       <c r="F131" t="n">
         <v>-6418.60769925926</v>
       </c>
       <c r="G131" t="n">
-        <v>-6429.239541574913</v>
+        <v>-6429.239541574912</v>
       </c>
     </row>
     <row r="132">
@@ -8950,13 +8950,13 @@
         <v>-358.22076163</v>
       </c>
       <c r="E135" t="n">
-        <v>-358.4814434255684</v>
+        <v>-358.4814434255685</v>
       </c>
       <c r="F135" t="n">
         <v>-6633.717807962963</v>
       </c>
       <c r="G135" t="n">
-        <v>-6638.545248621638</v>
+        <v>-6638.545248621639</v>
       </c>
     </row>
     <row r="136">
@@ -9000,13 +9000,13 @@
         <v>-360.82729632</v>
       </c>
       <c r="E137" t="n">
-        <v>-361.4027902147688</v>
+        <v>-361.4027902147689</v>
       </c>
       <c r="F137" t="n">
         <v>-6681.986968888889</v>
       </c>
       <c r="G137" t="n">
-        <v>-6692.644263236459</v>
+        <v>-6692.64426323646</v>
       </c>
     </row>
     <row r="138">
@@ -9150,13 +9150,13 @@
         <v>-349.44108375</v>
       </c>
       <c r="E143" t="n">
-        <v>-350.2448328023508</v>
+        <v>-350.2448328023507</v>
       </c>
       <c r="F143" t="n">
         <v>-6471.131180555555</v>
       </c>
       <c r="G143" t="n">
-        <v>-6486.015422265756</v>
+        <v>-6486.015422265755</v>
       </c>
     </row>
     <row r="144">
@@ -9200,13 +9200,13 @@
         <v>-351.01881719</v>
       </c>
       <c r="E145" t="n">
-        <v>-351.5119921580506</v>
+        <v>-351.5119921580507</v>
       </c>
       <c r="F145" t="n">
         <v>-6500.348466481481</v>
       </c>
       <c r="G145" t="n">
-        <v>-6509.481336260197</v>
+        <v>-6509.481336260198</v>
       </c>
     </row>
     <row r="146">
@@ -9231,7 +9231,7 @@
         <v>-6632.657368148149</v>
       </c>
       <c r="G146" t="n">
-        <v>-6644.711912208153</v>
+        <v>-6644.711912208151</v>
       </c>
     </row>
     <row r="147">
@@ -9250,13 +9250,13 @@
         <v>-359.32834585</v>
       </c>
       <c r="E147" t="n">
-        <v>-360.0730034399883</v>
+        <v>-360.0730034399881</v>
       </c>
       <c r="F147" t="n">
         <v>-6654.228626851852</v>
       </c>
       <c r="G147" t="n">
-        <v>-6668.018582222005</v>
+        <v>-6668.018582222002</v>
       </c>
     </row>
     <row r="148">
@@ -9275,13 +9275,13 @@
         <v>-347.99439697</v>
       </c>
       <c r="E148" t="n">
-        <v>-349.3412581118123</v>
+        <v>-349.3412581118122</v>
       </c>
       <c r="F148" t="n">
         <v>-6444.340684629629</v>
       </c>
       <c r="G148" t="n">
-        <v>-6469.282557626154</v>
+        <v>-6469.282557626152</v>
       </c>
     </row>
     <row r="149">
@@ -9325,13 +9325,13 @@
         <v>-357.22779913</v>
       </c>
       <c r="E150" t="n">
-        <v>-358.1264717290537</v>
+        <v>-358.1264717290536</v>
       </c>
       <c r="F150" t="n">
         <v>-6615.329613518518</v>
       </c>
       <c r="G150" t="n">
-        <v>-6631.971698686179</v>
+        <v>-6631.971698686178</v>
       </c>
     </row>
     <row r="151">
@@ -9406,7 +9406,7 @@
         <v>-6673.068361666667</v>
       </c>
       <c r="G153" t="n">
-        <v>-6683.30593821453</v>
+        <v>-6683.305938214529</v>
       </c>
     </row>
     <row r="154">
@@ -9456,7 +9456,7 @@
         <v>-6509.635962962963</v>
       </c>
       <c r="G155" t="n">
-        <v>-6523.872611553693</v>
+        <v>-6523.872611553694</v>
       </c>
     </row>
     <row r="156">
@@ -9581,7 +9581,7 @@
         <v>-6639.420017777778</v>
       </c>
       <c r="G160" t="n">
-        <v>-6649.530068584222</v>
+        <v>-6649.530068584221</v>
       </c>
     </row>
     <row r="161">
@@ -9600,13 +9600,13 @@
         <v>-355.10697324</v>
       </c>
       <c r="E161" t="n">
-        <v>-355.8112545800351</v>
+        <v>-355.8112545800352</v>
       </c>
       <c r="F161" t="n">
         <v>-6576.055060000001</v>
       </c>
       <c r="G161" t="n">
-        <v>-6589.097307037687</v>
+        <v>-6589.097307037689</v>
       </c>
     </row>
     <row r="162">
@@ -9631,7 +9631,7 @@
         <v>-6712.010290555556</v>
       </c>
       <c r="G162" t="n">
-        <v>-6636.844828275519</v>
+        <v>-6636.844828275517</v>
       </c>
     </row>
     <row r="163">
@@ -9675,13 +9675,13 @@
         <v>-361.58914159</v>
       </c>
       <c r="E164" t="n">
-        <v>-362.6161736562173</v>
+        <v>-362.6161736562172</v>
       </c>
       <c r="F164" t="n">
         <v>-6696.095214629629</v>
       </c>
       <c r="G164" t="n">
-        <v>-6715.114326966986</v>
+        <v>-6715.114326966985</v>
       </c>
     </row>
     <row r="165">
@@ -9750,13 +9750,13 @@
         <v>-352.46805444</v>
       </c>
       <c r="E167" t="n">
-        <v>-353.3544653545425</v>
+        <v>-353.3544653545424</v>
       </c>
       <c r="F167" t="n">
         <v>-6527.186193333333</v>
       </c>
       <c r="G167" t="n">
-        <v>-6543.601210269305</v>
+        <v>-6543.601210269304</v>
       </c>
     </row>
     <row r="168">
@@ -9775,13 +9775,13 @@
         <v>-357.73278889</v>
       </c>
       <c r="E168" t="n">
-        <v>-358.726290500573</v>
+        <v>-358.7262905005729</v>
       </c>
       <c r="F168" t="n">
         <v>-6624.68127574074</v>
       </c>
       <c r="G168" t="n">
-        <v>-6643.079453714315</v>
+        <v>-6643.079453714314</v>
       </c>
     </row>
     <row r="169">
@@ -9800,13 +9800,13 @@
         <v>-351.33761365</v>
       </c>
       <c r="E169" t="n">
-        <v>-352.5046587388033</v>
+        <v>-352.5046587388032</v>
       </c>
       <c r="F169" t="n">
         <v>-6506.252104629629</v>
       </c>
       <c r="G169" t="n">
-        <v>-6527.864050718579</v>
+        <v>-6527.864050718578</v>
       </c>
     </row>
     <row r="170">
@@ -9825,7 +9825,7 @@
         <v>-352.34824016</v>
       </c>
       <c r="E170" t="n">
-        <v>-352.9558347563906</v>
+        <v>-352.9558347563907</v>
       </c>
       <c r="F170" t="n">
         <v>-6524.96741037037</v>
@@ -9850,13 +9850,13 @@
         <v>-360.27259707</v>
       </c>
       <c r="E171" t="n">
-        <v>-360.985401516597</v>
+        <v>-360.9854015165969</v>
       </c>
       <c r="F171" t="n">
         <v>-6671.714760555556</v>
       </c>
       <c r="G171" t="n">
-        <v>-6684.914842899945</v>
+        <v>-6684.914842899943</v>
       </c>
     </row>
     <row r="172">
@@ -9931,7 +9931,7 @@
         <v>-6546.514769259259</v>
       </c>
       <c r="G174" t="n">
-        <v>-6562.673912827314</v>
+        <v>-6562.673912827312</v>
       </c>
     </row>
     <row r="175">
@@ -9950,13 +9950,13 @@
         <v>-353.85161311</v>
       </c>
       <c r="E175" t="n">
-        <v>-354.8619807892079</v>
+        <v>-354.8619807892077</v>
       </c>
       <c r="F175" t="n">
         <v>-6552.807650185186</v>
       </c>
       <c r="G175" t="n">
-        <v>-6571.518162763109</v>
+        <v>-6571.518162763106</v>
       </c>
     </row>
     <row r="176">
@@ -10006,7 +10006,7 @@
         <v>-6712.70314925926</v>
       </c>
       <c r="G177" t="n">
-        <v>-6724.199969707391</v>
+        <v>-6724.19996970739</v>
       </c>
     </row>
     <row r="178">
@@ -10050,13 +10050,13 @@
         <v>-356.86447928</v>
       </c>
       <c r="E179" t="n">
-        <v>-357.8724593966024</v>
+        <v>-357.8724593966025</v>
       </c>
       <c r="F179" t="n">
         <v>-6608.601468148148</v>
       </c>
       <c r="G179" t="n">
-        <v>-6627.267766603748</v>
+        <v>-6627.26776660375</v>
       </c>
     </row>
     <row r="180">
@@ -10075,7 +10075,7 @@
         <v>-361.75752284</v>
       </c>
       <c r="E180" t="n">
-        <v>-362.8551861152435</v>
+        <v>-362.8551861152434</v>
       </c>
       <c r="F180" t="n">
         <v>-6699.213385925926</v>
@@ -10150,13 +10150,13 @@
         <v>-359.09828233</v>
       </c>
       <c r="E183" t="n">
-        <v>-359.8350681009293</v>
+        <v>-359.8350681009292</v>
       </c>
       <c r="F183" t="n">
         <v>-6649.968191296297</v>
       </c>
       <c r="G183" t="n">
-        <v>-6663.61237223943</v>
+        <v>-6663.612372239429</v>
       </c>
     </row>
     <row r="184">
@@ -10275,7 +10275,7 @@
         <v>-355.42074312</v>
       </c>
       <c r="E188" t="n">
-        <v>-355.7741168646824</v>
+        <v>-355.7741168646823</v>
       </c>
       <c r="F188" t="n">
         <v>-6581.865613333333</v>
@@ -10375,13 +10375,13 @@
         <v>-358.81818973</v>
       </c>
       <c r="E192" t="n">
-        <v>-359.474751104479</v>
+        <v>-359.4747511044789</v>
       </c>
       <c r="F192" t="n">
         <v>-6644.781291296296</v>
       </c>
       <c r="G192" t="n">
-        <v>-6656.939835268129</v>
+        <v>-6656.939835268127</v>
       </c>
     </row>
     <row r="193">
@@ -10406,7 +10406,7 @@
         <v>-6501.954822962963</v>
       </c>
       <c r="G193" t="n">
-        <v>-6519.494097217877</v>
+        <v>-6519.494097217876</v>
       </c>
     </row>
     <row r="194">
@@ -10431,7 +10431,7 @@
         <v>-6634.44507574074</v>
       </c>
       <c r="G194" t="n">
-        <v>-6643.889843667126</v>
+        <v>-6643.889843667125</v>
       </c>
     </row>
     <row r="195">
@@ -10456,7 +10456,7 @@
         <v>-6636.142459074074</v>
       </c>
       <c r="G195" t="n">
-        <v>-6648.665892663277</v>
+        <v>-6648.665892663278</v>
       </c>
     </row>
     <row r="196">
@@ -10475,13 +10475,13 @@
         <v>-361.34859942</v>
       </c>
       <c r="E196" t="n">
-        <v>-362.3394629989125</v>
+        <v>-362.3394629989124</v>
       </c>
       <c r="F196" t="n">
         <v>-6691.640730000001</v>
       </c>
       <c r="G196" t="n">
-        <v>-6709.990055535417</v>
+        <v>-6709.990055535415</v>
       </c>
     </row>
     <row r="197">
@@ -10500,13 +10500,13 @@
         <v>-358.1006076</v>
       </c>
       <c r="E197" t="n">
-        <v>-359.1318008151178</v>
+        <v>-359.1318008151177</v>
       </c>
       <c r="F197" t="n">
         <v>-6631.492733333333</v>
       </c>
       <c r="G197" t="n">
-        <v>-6650.588903983663</v>
+        <v>-6650.588903983661</v>
       </c>
     </row>
     <row r="198">
@@ -10556,7 +10556,7 @@
         <v>-6710.797518518519</v>
       </c>
       <c r="G199" t="n">
-        <v>-6722.943604701236</v>
+        <v>-6722.943604701238</v>
       </c>
     </row>
     <row r="200">
@@ -10581,7 +10581,7 @@
         <v>-6581.452822962963</v>
       </c>
       <c r="G200" t="n">
-        <v>-6591.128322418014</v>
+        <v>-6591.128322418012</v>
       </c>
     </row>
     <row r="201">
@@ -10625,13 +10625,13 @@
         <v>-361.95135052</v>
       </c>
       <c r="E202" t="n">
-        <v>-362.6942609699548</v>
+        <v>-362.6942609699549</v>
       </c>
       <c r="F202" t="n">
         <v>-6702.802787407407</v>
       </c>
       <c r="G202" t="n">
-        <v>-6716.560388332496</v>
+        <v>-6716.560388332499</v>
       </c>
     </row>
     <row r="203">
@@ -10650,13 +10650,13 @@
         <v>-361.42887628</v>
       </c>
       <c r="E203" t="n">
-        <v>-362.316984761491</v>
+        <v>-362.3169847614909</v>
       </c>
       <c r="F203" t="n">
         <v>-6693.127338518519</v>
       </c>
       <c r="G203" t="n">
-        <v>-6709.573791879463</v>
+        <v>-6709.573791879461</v>
       </c>
     </row>
     <row r="204">
@@ -10675,13 +10675,13 @@
         <v>-358.31731139</v>
       </c>
       <c r="E204" t="n">
-        <v>-359.5850262509053</v>
+        <v>-359.5850262509055</v>
       </c>
       <c r="F204" t="n">
         <v>-6635.505766481481</v>
       </c>
       <c r="G204" t="n">
-        <v>-6658.981967609358</v>
+        <v>-6658.98196760936</v>
       </c>
     </row>
     <row r="205">
@@ -10781,7 +10781,7 @@
         <v>-6659.74552574074</v>
       </c>
       <c r="G208" t="n">
-        <v>-6671.928867299608</v>
+        <v>-6671.928867299606</v>
       </c>
     </row>
     <row r="209">
@@ -10856,7 +10856,7 @@
         <v>-6477.156910000001</v>
       </c>
       <c r="G211" t="n">
-        <v>-6499.428888407552</v>
+        <v>-6499.428888407551</v>
       </c>
     </row>
     <row r="212">
@@ -10875,13 +10875,13 @@
         <v>-361.39529663</v>
       </c>
       <c r="E212" t="n">
-        <v>-362.067906117675</v>
+        <v>-362.0679061176749</v>
       </c>
       <c r="F212" t="n">
         <v>-6692.505493148148</v>
       </c>
       <c r="G212" t="n">
-        <v>-6704.961224401388</v>
+        <v>-6704.961224401387</v>
       </c>
     </row>
     <row r="213">
@@ -10931,7 +10931,7 @@
         <v>-6673.073585555556</v>
       </c>
       <c r="G214" t="n">
-        <v>-6692.291921799942</v>
+        <v>-6692.291921799943</v>
       </c>
     </row>
     <row r="215">
@@ -10950,13 +10950,13 @@
         <v>-359.77364853</v>
       </c>
       <c r="E215" t="n">
-        <v>-360.5214110818952</v>
+        <v>-360.5214110818953</v>
       </c>
       <c r="F215" t="n">
         <v>-6662.474972777778</v>
       </c>
       <c r="G215" t="n">
-        <v>-6676.322427442505</v>
+        <v>-6676.322427442506</v>
       </c>
     </row>
     <row r="216">
@@ -11000,7 +11000,7 @@
         <v>-360.93327487</v>
       </c>
       <c r="E217" t="n">
-        <v>-361.7144708363548</v>
+        <v>-361.7144708363547</v>
       </c>
       <c r="F217" t="n">
         <v>-6683.949534629629</v>
@@ -11125,13 +11125,13 @@
         <v>-350.93357056</v>
       </c>
       <c r="E222" t="n">
-        <v>-351.7565935034672</v>
+        <v>-351.7565935034671</v>
       </c>
       <c r="F222" t="n">
         <v>-6498.769825185185</v>
       </c>
       <c r="G222" t="n">
-        <v>-6514.010990804947</v>
+        <v>-6514.010990804945</v>
       </c>
     </row>
     <row r="223">
@@ -11156,7 +11156,7 @@
         <v>-6643.388045</v>
       </c>
       <c r="G223" t="n">
-        <v>-6659.085561863617</v>
+        <v>-6659.085561863616</v>
       </c>
     </row>
     <row r="224">
@@ -11175,13 +11175,13 @@
         <v>-347.57263539</v>
       </c>
       <c r="E224" t="n">
-        <v>-348.2533198296759</v>
+        <v>-348.2533198296758</v>
       </c>
       <c r="F224" t="n">
         <v>-6436.530285</v>
       </c>
       <c r="G224" t="n">
-        <v>-6449.135552401405</v>
+        <v>-6449.135552401404</v>
       </c>
     </row>
     <row r="225">
@@ -11200,7 +11200,7 @@
         <v>-356.54256808</v>
       </c>
       <c r="E225" t="n">
-        <v>-357.0727245464288</v>
+        <v>-357.0727245464289</v>
       </c>
       <c r="F225" t="n">
         <v>-6602.640149629629</v>
@@ -11256,7 +11256,7 @@
         <v>-6660.135253703704</v>
       </c>
       <c r="G227" t="n">
-        <v>-6676.551747809977</v>
+        <v>-6676.551747809975</v>
       </c>
     </row>
     <row r="228">
@@ -11306,7 +11306,7 @@
         <v>-6496.55432</v>
       </c>
       <c r="G229" t="n">
-        <v>-6515.216879119899</v>
+        <v>-6515.2168791199</v>
       </c>
     </row>
     <row r="230">
@@ -11356,7 +11356,7 @@
         <v>-6685.489936666667</v>
       </c>
       <c r="G231" t="n">
-        <v>-6611.00741152019</v>
+        <v>-6611.007411520188</v>
       </c>
     </row>
     <row r="232">
@@ -11375,13 +11375,13 @@
         <v>-352.48530159</v>
       </c>
       <c r="E232" t="n">
-        <v>-352.9605882297768</v>
+        <v>-352.9605882297767</v>
       </c>
       <c r="F232" t="n">
         <v>-6527.505585</v>
       </c>
       <c r="G232" t="n">
-        <v>-6536.30718944031</v>
+        <v>-6536.307189440309</v>
       </c>
     </row>
     <row r="233">
@@ -11400,13 +11400,13 @@
         <v>-355.19843197</v>
       </c>
       <c r="E233" t="n">
-        <v>-356.0956540861997</v>
+        <v>-356.0956540861998</v>
       </c>
       <c r="F233" t="n">
         <v>-6577.748740185185</v>
       </c>
       <c r="G233" t="n">
-        <v>-6594.363964559254</v>
+        <v>-6594.363964559255</v>
       </c>
     </row>
     <row r="234">
@@ -11456,7 +11456,7 @@
         <v>-6537.168843518518</v>
       </c>
       <c r="G235" t="n">
-        <v>-6550.862700695697</v>
+        <v>-6550.862700695696</v>
       </c>
     </row>
     <row r="236">
@@ -11475,13 +11475,13 @@
         <v>-360.4185147</v>
       </c>
       <c r="E236" t="n">
-        <v>-360.9599274300728</v>
+        <v>-360.9599274300729</v>
       </c>
       <c r="F236" t="n">
         <v>-6674.416938888889</v>
       </c>
       <c r="G236" t="n">
-        <v>-6684.443100556904</v>
+        <v>-6684.443100556906</v>
       </c>
     </row>
     <row r="237">
@@ -11500,13 +11500,13 @@
         <v>-362.03007744</v>
       </c>
       <c r="E237" t="n">
-        <v>-362.7008264360661</v>
+        <v>-362.700826436066</v>
       </c>
       <c r="F237" t="n">
         <v>-6704.260693333334</v>
       </c>
       <c r="G237" t="n">
-        <v>-6716.681971038261</v>
+        <v>-6716.68197103826</v>
       </c>
     </row>
     <row r="238">
@@ -11556,7 +11556,7 @@
         <v>-6682.102247222222</v>
       </c>
       <c r="G239" t="n">
-        <v>-6620.802452695439</v>
+        <v>-6620.802452695437</v>
       </c>
     </row>
     <row r="240">
@@ -11625,13 +11625,13 @@
         <v>-355.05937572</v>
       </c>
       <c r="E242" t="n">
-        <v>-355.736388554386</v>
+        <v>-355.7363885543859</v>
       </c>
       <c r="F242" t="n">
         <v>-6575.173624444445</v>
       </c>
       <c r="G242" t="n">
-        <v>-6587.710899155296</v>
+        <v>-6587.710899155294</v>
       </c>
     </row>
     <row r="243">
@@ -11700,13 +11700,13 @@
         <v>-359.35100753</v>
       </c>
       <c r="E245" t="n">
-        <v>-360.0873528779508</v>
+        <v>-360.0873528779506</v>
       </c>
       <c r="F245" t="n">
         <v>-6654.648287592593</v>
       </c>
       <c r="G245" t="n">
-        <v>-6668.284312554643</v>
+        <v>-6668.284312554641</v>
       </c>
     </row>
     <row r="246">
@@ -11725,13 +11725,13 @@
         <v>-356.44114165</v>
       </c>
       <c r="E246" t="n">
-        <v>-357.0849212682557</v>
+        <v>-357.0849212682556</v>
       </c>
       <c r="F246" t="n">
         <v>-6600.761882407408</v>
       </c>
       <c r="G246" t="n">
-        <v>-6612.68372718992</v>
+        <v>-6612.683727189919</v>
       </c>
     </row>
     <row r="247">
@@ -11800,13 +11800,13 @@
         <v>-357.52283202</v>
       </c>
       <c r="E249" t="n">
-        <v>-358.2921086992222</v>
+        <v>-358.2921086992223</v>
       </c>
       <c r="F249" t="n">
         <v>-6620.793185555556</v>
       </c>
       <c r="G249" t="n">
-        <v>-6635.039049985597</v>
+        <v>-6635.039049985598</v>
       </c>
     </row>
     <row r="250">
@@ -11831,7 +11831,7 @@
         <v>-6543.046577037037</v>
       </c>
       <c r="G250" t="n">
-        <v>-6556.090265901243</v>
+        <v>-6556.090265901242</v>
       </c>
     </row>
     <row r="251">
@@ -11850,13 +11850,13 @@
         <v>-351.89510477</v>
       </c>
       <c r="E251" t="n">
-        <v>-352.3376179110093</v>
+        <v>-352.3376179110094</v>
       </c>
       <c r="F251" t="n">
         <v>-6516.576014259259</v>
       </c>
       <c r="G251" t="n">
-        <v>-6524.770702055726</v>
+        <v>-6524.77070205573</v>
       </c>
     </row>
     <row r="252">
@@ -11906,7 +11906,7 @@
         <v>-6566.621362592593</v>
       </c>
       <c r="G253" t="n">
-        <v>-6590.217784539192</v>
+        <v>-6590.217784539193</v>
       </c>
     </row>
     <row r="254">
@@ -11950,13 +11950,13 @@
         <v>-361.19308258</v>
       </c>
       <c r="E255" t="n">
-        <v>-361.6356166543856</v>
+        <v>-361.6356166543857</v>
       </c>
       <c r="F255" t="n">
         <v>-6688.760788518518</v>
       </c>
       <c r="G255" t="n">
-        <v>-6696.955863970104</v>
+        <v>-6696.955863970105</v>
       </c>
     </row>
     <row r="256">
@@ -11975,13 +11975,13 @@
         <v>-362.24209641</v>
       </c>
       <c r="E256" t="n">
-        <v>-363.044337340974</v>
+        <v>-363.0443373409741</v>
       </c>
       <c r="F256" t="n">
         <v>-6708.186970555555</v>
       </c>
       <c r="G256" t="n">
-        <v>-6723.043284092111</v>
+        <v>-6723.043284092112</v>
       </c>
     </row>
     <row r="257">
@@ -12000,13 +12000,13 @@
         <v>-362.12690136</v>
       </c>
       <c r="E257" t="n">
-        <v>-363.00057047581</v>
+        <v>-363.0005704758102</v>
       </c>
       <c r="F257" t="n">
         <v>-6706.053728888888</v>
       </c>
       <c r="G257" t="n">
-        <v>-6722.232786589075</v>
+        <v>-6722.232786589077</v>
       </c>
     </row>
     <row r="258">
@@ -12075,13 +12075,13 @@
         <v>-356.09538079</v>
       </c>
       <c r="E260" t="n">
-        <v>-356.5618041369661</v>
+        <v>-356.5618041369662</v>
       </c>
       <c r="F260" t="n">
         <v>-6594.358903518518</v>
       </c>
       <c r="G260" t="n">
-        <v>-6602.99637290678</v>
+        <v>-6602.996372906781</v>
       </c>
     </row>
     <row r="261">
@@ -12106,7 +12106,7 @@
         <v>-6571.90323537037</v>
       </c>
       <c r="G261" t="n">
-        <v>-6592.545206874779</v>
+        <v>-6592.545206874778</v>
       </c>
     </row>
     <row r="262">
@@ -12156,7 +12156,7 @@
         <v>-6584.103412037038</v>
       </c>
       <c r="G263" t="n">
-        <v>-6600.398779161997</v>
+        <v>-6600.398779161998</v>
       </c>
     </row>
     <row r="264">
@@ -12181,7 +12181,7 @@
         <v>-6569.462965555555</v>
       </c>
       <c r="G264" t="n">
-        <v>-6494.922346286597</v>
+        <v>-6494.922346286596</v>
       </c>
     </row>
     <row r="265">
@@ -12200,13 +12200,13 @@
         <v>-352.84399011</v>
       </c>
       <c r="E265" t="n">
-        <v>-353.739620933546</v>
+        <v>-353.7396209335461</v>
       </c>
       <c r="F265" t="n">
         <v>-6534.147965</v>
       </c>
       <c r="G265" t="n">
-        <v>-6550.733720991592</v>
+        <v>-6550.733720991593</v>
       </c>
     </row>
     <row r="266">
@@ -12250,13 +12250,13 @@
         <v>-356.2376948</v>
       </c>
       <c r="E267" t="n">
-        <v>-357.1831198524579</v>
+        <v>-357.1831198524578</v>
       </c>
       <c r="F267" t="n">
         <v>-6596.994348148148</v>
       </c>
       <c r="G267" t="n">
-        <v>-6614.502219489961</v>
+        <v>-6614.50221948996</v>
       </c>
     </row>
     <row r="268">
@@ -12275,13 +12275,13 @@
         <v>-357.80176412</v>
       </c>
       <c r="E268" t="n">
-        <v>-358.6616267085534</v>
+        <v>-358.6616267085533</v>
       </c>
       <c r="F268" t="n">
         <v>-6625.958594814814</v>
       </c>
       <c r="G268" t="n">
-        <v>-6641.881976084323</v>
+        <v>-6641.881976084322</v>
       </c>
     </row>
     <row r="269">
@@ -12306,7 +12306,7 @@
         <v>-6600.281019444445</v>
       </c>
       <c r="G269" t="n">
-        <v>-6606.493563537498</v>
+        <v>-6606.493563537499</v>
       </c>
     </row>
     <row r="270">
@@ -12325,13 +12325,13 @@
         <v>-355.5830248</v>
       </c>
       <c r="E270" t="n">
-        <v>-355.9430763218795</v>
+        <v>-355.9430763218794</v>
       </c>
       <c r="F270" t="n">
         <v>-6584.870829629629</v>
       </c>
       <c r="G270" t="n">
-        <v>-6591.538450405176</v>
+        <v>-6591.538450405174</v>
       </c>
     </row>
     <row r="271">
@@ -12375,13 +12375,13 @@
         <v>-351.1397039</v>
       </c>
       <c r="E272" t="n">
-        <v>-351.6239882714904</v>
+        <v>-351.6239882714903</v>
       </c>
       <c r="F272" t="n">
         <v>-6502.587109259259</v>
       </c>
       <c r="G272" t="n">
-        <v>-6511.555338360933</v>
+        <v>-6511.555338360932</v>
       </c>
     </row>
     <row r="273">
@@ -12500,13 +12500,13 @@
         <v>-355.62140019</v>
       </c>
       <c r="E277" t="n">
-        <v>-356.4186980406781</v>
+        <v>-356.418698040678</v>
       </c>
       <c r="F277" t="n">
         <v>-6585.581484999999</v>
       </c>
       <c r="G277" t="n">
-        <v>-6600.346260012557</v>
+        <v>-6600.346260012556</v>
       </c>
     </row>
     <row r="278">
@@ -12525,13 +12525,13 @@
         <v>-362.11058414</v>
       </c>
       <c r="E278" t="n">
-        <v>-362.7067571725642</v>
+        <v>-362.7067571725641</v>
       </c>
       <c r="F278" t="n">
         <v>-6705.751558148148</v>
       </c>
       <c r="G278" t="n">
-        <v>-6716.791799491929</v>
+        <v>-6716.791799491928</v>
       </c>
     </row>
     <row r="279">
@@ -12656,7 +12656,7 @@
         <v>-6654.837757407407</v>
       </c>
       <c r="G283" t="n">
-        <v>-6669.636542501811</v>
+        <v>-6669.636542501812</v>
       </c>
     </row>
     <row r="284">
@@ -12675,13 +12675,13 @@
         <v>-352.88761684</v>
       </c>
       <c r="E284" t="n">
-        <v>-353.7238549480327</v>
+        <v>-353.7238549480326</v>
       </c>
       <c r="F284" t="n">
         <v>-6534.955867407408</v>
       </c>
       <c r="G284" t="n">
-        <v>-6550.441758296902</v>
+        <v>-6550.4417582969</v>
       </c>
     </row>
     <row r="285">
@@ -12750,13 +12750,13 @@
         <v>-349.12019873</v>
       </c>
       <c r="E287" t="n">
-        <v>-350.3098506229355</v>
+        <v>-350.3098506229356</v>
       </c>
       <c r="F287" t="n">
         <v>-6465.188865370371</v>
       </c>
       <c r="G287" t="n">
-        <v>-6487.219455980287</v>
+        <v>-6487.219455980288</v>
       </c>
     </row>
     <row r="288">
@@ -12781,7 +12781,7 @@
         <v>-6685.611890925926</v>
       </c>
       <c r="G288" t="n">
-        <v>-6698.917996931907</v>
+        <v>-6698.917996931905</v>
       </c>
     </row>
     <row r="289">
@@ -12831,7 +12831,7 @@
         <v>-6540.851737407407</v>
       </c>
       <c r="G290" t="n">
-        <v>-6563.046820484252</v>
+        <v>-6563.046820484253</v>
       </c>
     </row>
     <row r="291">
@@ -12875,13 +12875,13 @@
         <v>-357.66600488</v>
       </c>
       <c r="E292" t="n">
-        <v>-358.8018876599356</v>
+        <v>-358.8018876599355</v>
       </c>
       <c r="F292" t="n">
         <v>-6623.444534814816</v>
       </c>
       <c r="G292" t="n">
-        <v>-6644.479401109918</v>
+        <v>-6644.479401109917</v>
       </c>
     </row>
     <row r="293">
@@ -12925,13 +12925,13 @@
         <v>-352.38228694</v>
       </c>
       <c r="E294" t="n">
-        <v>-353.6781914682604</v>
+        <v>-353.6781914682603</v>
       </c>
       <c r="F294" t="n">
         <v>-6525.597906296295</v>
       </c>
       <c r="G294" t="n">
-        <v>-6549.596138301118</v>
+        <v>-6549.596138301117</v>
       </c>
     </row>
     <row r="295">
@@ -13006,7 +13006,7 @@
         <v>-6597.822222407407</v>
       </c>
       <c r="G297" t="n">
-        <v>-6610.852560787792</v>
+        <v>-6610.85256078779</v>
       </c>
     </row>
     <row r="298">
@@ -13075,13 +13075,13 @@
         <v>-355.71859977</v>
       </c>
       <c r="E300" t="n">
-        <v>-356.6128264674476</v>
+        <v>-356.6128264674475</v>
       </c>
       <c r="F300" t="n">
         <v>-6587.381477222223</v>
       </c>
       <c r="G300" t="n">
-        <v>-6603.94123087866</v>
+        <v>-6603.941230878658</v>
       </c>
     </row>
     <row r="301">
@@ -13131,7 +13131,7 @@
         <v>-6701.378289814814</v>
       </c>
       <c r="G302" t="n">
-        <v>-6709.188829498447</v>
+        <v>-6709.188829498446</v>
       </c>
     </row>
     <row r="303">
@@ -13181,7 +13181,7 @@
         <v>-6594.266464444444</v>
       </c>
       <c r="G304" t="n">
-        <v>-6610.615414991879</v>
+        <v>-6610.615414991878</v>
       </c>
     </row>
     <row r="305">
@@ -13206,7 +13206,7 @@
         <v>-6541.424572962963</v>
       </c>
       <c r="G305" t="n">
-        <v>-6559.688903888383</v>
+        <v>-6559.688903888381</v>
       </c>
     </row>
     <row r="306">
@@ -13250,13 +13250,13 @@
         <v>-359.61217994</v>
       </c>
       <c r="E307" t="n">
-        <v>-360.1690893016368</v>
+        <v>-360.1690893016369</v>
       </c>
       <c r="F307" t="n">
         <v>-6659.484813703703</v>
       </c>
       <c r="G307" t="n">
-        <v>-6669.797950030311</v>
+        <v>-6669.797950030312</v>
       </c>
     </row>
     <row r="308">
@@ -13306,7 +13306,7 @@
         <v>-6674.533409629629</v>
       </c>
       <c r="G309" t="n">
-        <v>-6686.813289212191</v>
+        <v>-6686.81328921219</v>
       </c>
     </row>
     <row r="310">
@@ -13331,7 +13331,7 @@
         <v>-6620.349261851852</v>
       </c>
       <c r="G310" t="n">
-        <v>-6633.298824474203</v>
+        <v>-6633.298824474204</v>
       </c>
     </row>
     <row r="311">
@@ -13375,13 +13375,13 @@
         <v>-352.75622344</v>
       </c>
       <c r="E312" t="n">
-        <v>-353.2595883193766</v>
+        <v>-353.2595883193765</v>
       </c>
       <c r="F312" t="n">
         <v>-6532.522656296296</v>
       </c>
       <c r="G312" t="n">
-        <v>-6541.844228136603</v>
+        <v>-6541.844228136602</v>
       </c>
     </row>
     <row r="313">
@@ -13400,13 +13400,13 @@
         <v>-358.43563679</v>
       </c>
       <c r="E313" t="n">
-        <v>-359.0420942169165</v>
+        <v>-359.0420942169164</v>
       </c>
       <c r="F313" t="n">
         <v>-6637.696977592593</v>
       </c>
       <c r="G313" t="n">
-        <v>-6648.927670683638</v>
+        <v>-6648.927670683637</v>
       </c>
     </row>
     <row r="314">
@@ -13425,7 +13425,7 @@
         <v>-353.77282646</v>
       </c>
       <c r="E314" t="n">
-        <v>-354.4353376200582</v>
+        <v>-354.4353376200581</v>
       </c>
       <c r="F314" t="n">
         <v>-6551.348638148147</v>
@@ -13506,7 +13506,7 @@
         <v>-6559.433692962963</v>
       </c>
       <c r="G317" t="n">
-        <v>-6585.738817199417</v>
+        <v>-6585.738817199416</v>
       </c>
     </row>
     <row r="318">
@@ -13525,13 +13525,13 @@
         <v>-360.5193526</v>
       </c>
       <c r="E318" t="n">
-        <v>-361.4670610922125</v>
+        <v>-361.4670610922126</v>
       </c>
       <c r="F318" t="n">
         <v>-6676.284307407407</v>
       </c>
       <c r="G318" t="n">
-        <v>-6693.834464670602</v>
+        <v>-6693.834464670603</v>
       </c>
     </row>
     <row r="319">
@@ -13625,13 +13625,13 @@
         <v>-358.41770865</v>
       </c>
       <c r="E322" t="n">
-        <v>-359.0875449056784</v>
+        <v>-359.0875449056783</v>
       </c>
       <c r="F322" t="n">
         <v>-6637.364975</v>
       </c>
       <c r="G322" t="n">
-        <v>-6649.769350105156</v>
+        <v>-6649.769350105154</v>
       </c>
     </row>
     <row r="323">
@@ -13675,13 +13675,13 @@
         <v>-361.82263639</v>
       </c>
       <c r="E324" t="n">
-        <v>-362.8809972856459</v>
+        <v>-362.8809972856458</v>
       </c>
       <c r="F324" t="n">
         <v>-6700.419192407408</v>
       </c>
       <c r="G324" t="n">
-        <v>-6720.018468252702</v>
+        <v>-6720.0184682527</v>
       </c>
     </row>
     <row r="325">
@@ -13700,13 +13700,13 @@
         <v>-360.5812955</v>
       </c>
       <c r="E325" t="n">
-        <v>-361.2613326077339</v>
+        <v>-361.261332607734</v>
       </c>
       <c r="F325" t="n">
         <v>-6677.431398148148</v>
       </c>
       <c r="G325" t="n">
-        <v>-6690.024677920999</v>
+        <v>-6690.024677921</v>
       </c>
     </row>
     <row r="326">
@@ -13725,13 +13725,13 @@
         <v>-348.51480635</v>
       </c>
       <c r="E326" t="n">
-        <v>-349.1663036589601</v>
+        <v>-349.16630365896</v>
       </c>
       <c r="F326" t="n">
         <v>-6453.977895370371</v>
       </c>
       <c r="G326" t="n">
-        <v>-6466.042660351113</v>
+        <v>-6466.042660351111</v>
       </c>
     </row>
     <row r="327">
@@ -13756,7 +13756,7 @@
         <v>-6687.491889444444</v>
       </c>
       <c r="G327" t="n">
-        <v>-6701.686545399887</v>
+        <v>-6701.686545399886</v>
       </c>
     </row>
     <row r="328">
@@ -13775,13 +13775,13 @@
         <v>-358.36135436</v>
       </c>
       <c r="E328" t="n">
-        <v>-358.9862568790275</v>
+        <v>-358.9862568790274</v>
       </c>
       <c r="F328" t="n">
         <v>-6636.321377037037</v>
       </c>
       <c r="G328" t="n">
-        <v>-6647.893645907916</v>
+        <v>-6647.893645907915</v>
       </c>
     </row>
     <row r="329">
@@ -13800,13 +13800,13 @@
         <v>-357.72310762</v>
       </c>
       <c r="E329" t="n">
-        <v>-358.2619317485014</v>
+        <v>-358.2619317485013</v>
       </c>
       <c r="F329" t="n">
         <v>-6624.501992962963</v>
       </c>
       <c r="G329" t="n">
-        <v>-6634.48021756484</v>
+        <v>-6634.480217564839</v>
       </c>
     </row>
     <row r="330">
@@ -13831,7 +13831,7 @@
         <v>-6650.087916666667</v>
       </c>
       <c r="G330" t="n">
-        <v>-6579.348013291909</v>
+        <v>-6579.34801329191</v>
       </c>
     </row>
     <row r="331">
@@ -13856,7 +13856,7 @@
         <v>-6635.956606666667</v>
       </c>
       <c r="G331" t="n">
-        <v>-6653.858086939958</v>
+        <v>-6653.858086939959</v>
       </c>
     </row>
     <row r="332">
@@ -13875,13 +13875,13 @@
         <v>-354.90901634</v>
       </c>
       <c r="E332" t="n">
-        <v>-355.5564004292158</v>
+        <v>-355.5564004292159</v>
       </c>
       <c r="F332" t="n">
         <v>-6572.389191481481</v>
       </c>
       <c r="G332" t="n">
-        <v>-6584.377785726219</v>
+        <v>-6584.377785726221</v>
       </c>
     </row>
     <row r="333">
@@ -13900,13 +13900,13 @@
         <v>-359.35936203</v>
       </c>
       <c r="E333" t="n">
-        <v>-359.7753084858311</v>
+        <v>-359.775308485831</v>
       </c>
       <c r="F333" t="n">
         <v>-6654.803000555556</v>
       </c>
       <c r="G333" t="n">
-        <v>-6662.505712700576</v>
+        <v>-6662.505712700575</v>
       </c>
     </row>
     <row r="334">
@@ -14006,7 +14006,7 @@
         <v>-6707.954095555556</v>
       </c>
       <c r="G337" t="n">
-        <v>-6728.620038004441</v>
+        <v>-6728.62003800444</v>
       </c>
     </row>
     <row r="338">
@@ -14075,13 +14075,13 @@
         <v>-360.45142907</v>
       </c>
       <c r="E340" t="n">
-        <v>-361.0264400680652</v>
+        <v>-361.0264400680651</v>
       </c>
       <c r="F340" t="n">
         <v>-6675.026464259259</v>
       </c>
       <c r="G340" t="n">
-        <v>-6685.674816075281</v>
+        <v>-6685.67481607528</v>
       </c>
     </row>
     <row r="341">
@@ -14100,13 +14100,13 @@
         <v>-360.55934518</v>
       </c>
       <c r="E341" t="n">
-        <v>-361.4375401427792</v>
+        <v>-361.4375401427791</v>
       </c>
       <c r="F341" t="n">
         <v>-6677.024910740741</v>
       </c>
       <c r="G341" t="n">
-        <v>-6693.287780421837</v>
+        <v>-6693.287780421836</v>
       </c>
     </row>
     <row r="342">
@@ -14125,13 +14125,13 @@
         <v>-354.79723302</v>
       </c>
       <c r="E342" t="n">
-        <v>-355.1158715544789</v>
+        <v>-355.1158715544788</v>
       </c>
       <c r="F342" t="n">
         <v>-6570.319130000001</v>
       </c>
       <c r="G342" t="n">
-        <v>-6576.219843601461</v>
+        <v>-6576.21984360146</v>
       </c>
     </row>
     <row r="343">
@@ -14156,7 +14156,7 @@
         <v>-6697.978932777778</v>
       </c>
       <c r="G343" t="n">
-        <v>-6613.148875554918</v>
+        <v>-6613.148875554916</v>
       </c>
     </row>
     <row r="344">
@@ -14175,13 +14175,13 @@
         <v>-357.89701701</v>
       </c>
       <c r="E344" t="n">
-        <v>-358.3364795909782</v>
+        <v>-358.3364795909781</v>
       </c>
       <c r="F344" t="n">
         <v>-6627.722537222223</v>
       </c>
       <c r="G344" t="n">
-        <v>-6635.860733166263</v>
+        <v>-6635.860733166262</v>
       </c>
     </row>
     <row r="345">
@@ -14250,13 +14250,13 @@
         <v>-351.57729135</v>
       </c>
       <c r="E347" t="n">
-        <v>-352.1247888535062</v>
+        <v>-352.1247888535063</v>
       </c>
       <c r="F347" t="n">
         <v>-6510.690580555556</v>
       </c>
       <c r="G347" t="n">
-        <v>-6520.829423213078</v>
+        <v>-6520.829423213079</v>
       </c>
     </row>
     <row r="348">
@@ -14275,13 +14275,13 @@
         <v>-352.52110953</v>
       </c>
       <c r="E348" t="n">
-        <v>-353.1844230060119</v>
+        <v>-353.1844230060118</v>
       </c>
       <c r="F348" t="n">
         <v>-6528.168695</v>
       </c>
       <c r="G348" t="n">
-        <v>-6540.452277889109</v>
+        <v>-6540.452277889108</v>
       </c>
     </row>
     <row r="349">
@@ -14306,7 +14306,7 @@
         <v>-6537.24166037037</v>
       </c>
       <c r="G349" t="n">
-        <v>-6553.635773173722</v>
+        <v>-6553.635773173721</v>
       </c>
     </row>
     <row r="350">
@@ -14356,7 +14356,7 @@
         <v>-6620.886794814815</v>
       </c>
       <c r="G351" t="n">
-        <v>-6629.603812980804</v>
+        <v>-6629.603812980803</v>
       </c>
     </row>
     <row r="352">
@@ -14375,13 +14375,13 @@
         <v>-353.67911456</v>
       </c>
       <c r="E352" t="n">
-        <v>-354.5545578006086</v>
+        <v>-354.5545578006084</v>
       </c>
       <c r="F352" t="n">
         <v>-6549.613232592593</v>
       </c>
       <c r="G352" t="n">
-        <v>-6565.825144455715</v>
+        <v>-6565.825144455712</v>
       </c>
     </row>
     <row r="353">
@@ -14400,13 +14400,13 @@
         <v>-345.9256201</v>
       </c>
       <c r="E353" t="n">
-        <v>-348.3845544578098</v>
+        <v>-348.3845544578097</v>
       </c>
       <c r="F353" t="n">
         <v>-6406.030001851852</v>
       </c>
       <c r="G353" t="n">
-        <v>-6451.565823292774</v>
+        <v>-6451.565823292773</v>
       </c>
     </row>
     <row r="354">
@@ -14425,13 +14425,13 @@
         <v>-356.35551207</v>
       </c>
       <c r="E354" t="n">
-        <v>-357.1274947935316</v>
+        <v>-357.1274947935315</v>
       </c>
       <c r="F354" t="n">
         <v>-6599.176149444444</v>
       </c>
       <c r="G354" t="n">
-        <v>-6613.472125806141</v>
+        <v>-6613.47212580614</v>
       </c>
     </row>
     <row r="355">
@@ -14450,13 +14450,13 @@
         <v>-358.83870478</v>
       </c>
       <c r="E355" t="n">
-        <v>-359.8288844345428</v>
+        <v>-359.8288844345427</v>
       </c>
       <c r="F355" t="n">
         <v>-6645.161199629631</v>
       </c>
       <c r="G355" t="n">
-        <v>-6663.497859898941</v>
+        <v>-6663.497859898939</v>
       </c>
     </row>
     <row r="356">
@@ -14531,7 +14531,7 @@
         <v>-6522.63607</v>
       </c>
       <c r="G358" t="n">
-        <v>-6539.161566208152</v>
+        <v>-6539.161566208151</v>
       </c>
     </row>
     <row r="359">
@@ -14700,13 +14700,13 @@
         <v>-351.71595871</v>
       </c>
       <c r="E365" t="n">
-        <v>-352.912891172682</v>
+        <v>-352.9128911726819</v>
       </c>
       <c r="F365" t="n">
         <v>-6513.258494629629</v>
       </c>
       <c r="G365" t="n">
-        <v>-6535.423910605221</v>
+        <v>-6535.42391060522</v>
       </c>
     </row>
     <row r="366">
@@ -14725,13 +14725,13 @@
         <v>-360.54684041</v>
       </c>
       <c r="E366" t="n">
-        <v>-361.5969008765172</v>
+        <v>-361.5969008765173</v>
       </c>
       <c r="F366" t="n">
         <v>-6676.793340925926</v>
       </c>
       <c r="G366" t="n">
-        <v>-6696.238905120689</v>
+        <v>-6696.238905120691</v>
       </c>
     </row>
     <row r="367">
@@ -14806,7 +14806,7 @@
         <v>-6633.47156</v>
       </c>
       <c r="G369" t="n">
-        <v>-6645.113183394218</v>
+        <v>-6645.113183394219</v>
       </c>
     </row>
     <row r="370">
@@ -14856,7 +14856,7 @@
         <v>-6609.262531111111</v>
       </c>
       <c r="G371" t="n">
-        <v>-6623.003618128543</v>
+        <v>-6623.003618128541</v>
       </c>
     </row>
     <row r="372">
@@ -14881,7 +14881,7 @@
         <v>-6693.761393888889</v>
       </c>
       <c r="G372" t="n">
-        <v>-6705.827654232078</v>
+        <v>-6705.827654232077</v>
       </c>
     </row>
     <row r="373">
@@ -14925,13 +14925,13 @@
         <v>-353.43565812</v>
       </c>
       <c r="E374" t="n">
-        <v>-354.1735257177686</v>
+        <v>-354.1735257177685</v>
       </c>
       <c r="F374" t="n">
         <v>-6545.104780000001</v>
       </c>
       <c r="G374" t="n">
-        <v>-6558.768994773493</v>
+        <v>-6558.768994773492</v>
       </c>
     </row>
     <row r="375">
@@ -14950,13 +14950,13 @@
         <v>-358.83891197</v>
       </c>
       <c r="E375" t="n">
-        <v>-359.3470200286489</v>
+        <v>-359.347020028649</v>
       </c>
       <c r="F375" t="n">
         <v>-6645.165036481481</v>
       </c>
       <c r="G375" t="n">
-        <v>-6654.57444497498</v>
+        <v>-6654.574444974981</v>
       </c>
     </row>
     <row r="376">
@@ -15006,7 +15006,7 @@
         <v>-6593.255537407408</v>
       </c>
       <c r="G377" t="n">
-        <v>-6606.387849071743</v>
+        <v>-6606.387849071742</v>
       </c>
     </row>
     <row r="378">
@@ -15100,13 +15100,13 @@
         <v>-352.54310634</v>
       </c>
       <c r="E381" t="n">
-        <v>-353.1456092575829</v>
+        <v>-353.1456092575828</v>
       </c>
       <c r="F381" t="n">
         <v>-6528.576043333333</v>
       </c>
       <c r="G381" t="n">
-        <v>-6539.733504770054</v>
+        <v>-6539.733504770052</v>
       </c>
     </row>
     <row r="382">
@@ -15125,7 +15125,7 @@
         <v>-355.15466457</v>
       </c>
       <c r="E382" t="n">
-        <v>-355.8350480175768</v>
+        <v>-355.8350480175769</v>
       </c>
       <c r="F382" t="n">
         <v>-6576.938232777778</v>
@@ -15175,13 +15175,13 @@
         <v>-360.53356462</v>
       </c>
       <c r="E384" t="n">
-        <v>-361.3974235298921</v>
+        <v>-361.3974235298922</v>
       </c>
       <c r="F384" t="n">
         <v>-6676.547492962964</v>
       </c>
       <c r="G384" t="n">
-        <v>-6692.544880183187</v>
+        <v>-6692.544880183188</v>
       </c>
     </row>
     <row r="385">
@@ -15206,7 +15206,7 @@
         <v>-6644.375417407408</v>
       </c>
       <c r="G385" t="n">
-        <v>-6663.884357916983</v>
+        <v>-6663.884357916982</v>
       </c>
     </row>
     <row r="386">
@@ -15231,7 +15231,7 @@
         <v>-6674.405301111111</v>
       </c>
       <c r="G386" t="n">
-        <v>-6605.96072354591</v>
+        <v>-6605.960723545912</v>
       </c>
     </row>
     <row r="387">
@@ -15275,13 +15275,13 @@
         <v>-356.58340176</v>
       </c>
       <c r="E388" t="n">
-        <v>-357.3355748378701</v>
+        <v>-357.33557483787</v>
       </c>
       <c r="F388" t="n">
         <v>-6603.39632888889</v>
       </c>
       <c r="G388" t="n">
-        <v>-6617.325459960558</v>
+        <v>-6617.325459960556</v>
       </c>
     </row>
     <row r="389">
@@ -15306,7 +15306,7 @@
         <v>-6665.43741037037</v>
       </c>
       <c r="G389" t="n">
-        <v>-6680.6634336886</v>
+        <v>-6680.663433688599</v>
       </c>
     </row>
     <row r="390">
@@ -15381,7 +15381,7 @@
         <v>-6516.89675111111</v>
       </c>
       <c r="G392" t="n">
-        <v>-6526.347224190552</v>
+        <v>-6526.347224190551</v>
       </c>
     </row>
     <row r="393">
@@ -15400,13 +15400,13 @@
         <v>-356.78537083</v>
       </c>
       <c r="E393" t="n">
-        <v>-357.6102392332094</v>
+        <v>-357.6102392332093</v>
       </c>
       <c r="F393" t="n">
         <v>-6607.136496851851</v>
       </c>
       <c r="G393" t="n">
-        <v>-6622.411837652025</v>
+        <v>-6622.411837652024</v>
       </c>
     </row>
     <row r="394">
@@ -15425,13 +15425,13 @@
         <v>-352.6326487</v>
       </c>
       <c r="E394" t="n">
-        <v>-353.3205751157978</v>
+        <v>-353.3205751157979</v>
       </c>
       <c r="F394" t="n">
         <v>-6530.234235185186</v>
       </c>
       <c r="G394" t="n">
-        <v>-6542.973613255515</v>
+        <v>-6542.973613255516</v>
       </c>
     </row>
     <row r="395">
@@ -15531,7 +15531,7 @@
         <v>-6553.874024999999</v>
       </c>
       <c r="G398" t="n">
-        <v>-6557.683580312476</v>
+        <v>-6557.683580312475</v>
       </c>
     </row>
     <row r="399">
@@ -15650,13 +15650,13 @@
         <v>-120.6564741</v>
       </c>
       <c r="E403" t="n">
-        <v>-119.1646760375624</v>
+        <v>-119.1646760375623</v>
       </c>
       <c r="F403" t="n">
         <v>-6703.137449999999</v>
       </c>
       <c r="G403" t="n">
-        <v>-6620.259779864577</v>
+        <v>-6620.259779864575</v>
       </c>
     </row>
     <row r="404">
@@ -15675,13 +15675,13 @@
         <v>-357.69553521</v>
       </c>
       <c r="E404" t="n">
-        <v>-358.4915844771551</v>
+        <v>-358.4915844771553</v>
       </c>
       <c r="F404" t="n">
         <v>-6623.991392777778</v>
       </c>
       <c r="G404" t="n">
-        <v>-6638.733045873243</v>
+        <v>-6638.733045873246</v>
       </c>
     </row>
     <row r="405">
@@ -15700,13 +15700,13 @@
         <v>-360.46777484</v>
       </c>
       <c r="E405" t="n">
-        <v>-361.1334790003764</v>
+        <v>-361.1334790003763</v>
       </c>
       <c r="F405" t="n">
         <v>-6675.329163703705</v>
       </c>
       <c r="G405" t="n">
-        <v>-6687.657018525489</v>
+        <v>-6687.657018525487</v>
       </c>
     </row>
     <row r="406">
@@ -15725,7 +15725,7 @@
         <v>-359.35636577</v>
       </c>
       <c r="E406" t="n">
-        <v>-359.6400207176267</v>
+        <v>-359.6400207176266</v>
       </c>
       <c r="F406" t="n">
         <v>-6654.74751425926</v>
@@ -15750,13 +15750,13 @@
         <v>-361.89780774</v>
       </c>
       <c r="E407" t="n">
-        <v>-362.7771009455264</v>
+        <v>-362.7771009455262</v>
       </c>
       <c r="F407" t="n">
         <v>-6701.811254444445</v>
       </c>
       <c r="G407" t="n">
-        <v>-6718.094461954192</v>
+        <v>-6718.094461954189</v>
       </c>
     </row>
     <row r="408">
@@ -15800,13 +15800,13 @@
         <v>-357.92061138</v>
       </c>
       <c r="E409" t="n">
-        <v>-358.7224523214511</v>
+        <v>-358.7224523214512</v>
       </c>
       <c r="F409" t="n">
         <v>-6628.159470000001</v>
       </c>
       <c r="G409" t="n">
-        <v>-6643.008376323169</v>
+        <v>-6643.008376323171</v>
       </c>
     </row>
     <row r="410">
@@ -15875,13 +15875,13 @@
         <v>-358.3457297</v>
       </c>
       <c r="E412" t="n">
-        <v>-358.8682455376367</v>
+        <v>-358.8682455376366</v>
       </c>
       <c r="F412" t="n">
         <v>-6636.032031481481</v>
       </c>
       <c r="G412" t="n">
-        <v>-6645.708250696975</v>
+        <v>-6645.708250696974</v>
       </c>
     </row>
     <row r="413">
@@ -15950,7 +15950,7 @@
         <v>-359.29146083</v>
       </c>
       <c r="E415" t="n">
-        <v>-360.4147313876127</v>
+        <v>-360.4147313876126</v>
       </c>
       <c r="F415" t="n">
         <v>-6653.545570925926</v>
@@ -15981,7 +15981,7 @@
         <v>-6520.570483518519</v>
       </c>
       <c r="G416" t="n">
-        <v>-6537.823812331352</v>
+        <v>-6537.823812331351</v>
       </c>
     </row>
     <row r="417">
@@ -16025,13 +16025,13 @@
         <v>-361.72584269</v>
       </c>
       <c r="E418" t="n">
-        <v>-362.2397456345494</v>
+        <v>-362.2397456345493</v>
       </c>
       <c r="F418" t="n">
         <v>-6698.626716481481</v>
       </c>
       <c r="G418" t="n">
-        <v>-6708.14343767684</v>
+        <v>-6708.143437676838</v>
       </c>
     </row>
     <row r="419">
@@ -16050,13 +16050,13 @@
         <v>-358.39135575</v>
       </c>
       <c r="E419" t="n">
-        <v>-358.7895648980364</v>
+        <v>-358.7895648980362</v>
       </c>
       <c r="F419" t="n">
         <v>-6636.876958333333</v>
       </c>
       <c r="G419" t="n">
-        <v>-6644.251201815488</v>
+        <v>-6644.251201815485</v>
       </c>
     </row>
     <row r="420">
@@ -16081,7 +16081,7 @@
         <v>-6651.085824629629</v>
       </c>
       <c r="G420" t="n">
-        <v>-6661.588463952949</v>
+        <v>-6661.588463952948</v>
       </c>
     </row>
     <row r="421">
@@ -16175,13 +16175,13 @@
         <v>-360.38371761</v>
       </c>
       <c r="E424" t="n">
-        <v>-360.9849109578418</v>
+        <v>-360.9849109578419</v>
       </c>
       <c r="F424" t="n">
         <v>-6673.772548333333</v>
       </c>
       <c r="G424" t="n">
-        <v>-6684.905758478551</v>
+        <v>-6684.905758478552</v>
       </c>
     </row>
     <row r="425">
@@ -16231,7 +16231,7 @@
         <v>-6670.28853462963</v>
       </c>
       <c r="G426" t="n">
-        <v>-6686.103807945612</v>
+        <v>-6686.103807945611</v>
       </c>
     </row>
     <row r="427">
@@ -16350,13 +16350,13 @@
         <v>-358.93973384</v>
       </c>
       <c r="E431" t="n">
-        <v>-359.5553261341358</v>
+        <v>-359.5553261341357</v>
       </c>
       <c r="F431" t="n">
         <v>-6647.032108148148</v>
       </c>
       <c r="G431" t="n">
-        <v>-6658.431965446959</v>
+        <v>-6658.431965446957</v>
       </c>
     </row>
     <row r="432">
@@ -16425,13 +16425,13 @@
         <v>-352.72313346</v>
       </c>
       <c r="E434" t="n">
-        <v>-353.4705652230865</v>
+        <v>-353.4705652230866</v>
       </c>
       <c r="F434" t="n">
         <v>-6531.909878888889</v>
       </c>
       <c r="G434" t="n">
-        <v>-6545.751207834935</v>
+        <v>-6545.751207834936</v>
       </c>
     </row>
     <row r="435">
@@ -16556,7 +16556,7 @@
         <v>-6620.112052407408</v>
       </c>
       <c r="G439" t="n">
-        <v>-6632.959876275981</v>
+        <v>-6632.959876275979</v>
       </c>
     </row>
     <row r="440">
@@ -16625,13 +16625,13 @@
         <v>-360.97043986</v>
       </c>
       <c r="E442" t="n">
-        <v>-361.7323352641416</v>
+        <v>-361.7323352641417</v>
       </c>
       <c r="F442" t="n">
         <v>-6684.637775185185</v>
       </c>
       <c r="G442" t="n">
-        <v>-6698.746949335956</v>
+        <v>-6698.746949335957</v>
       </c>
     </row>
     <row r="443">
@@ -16675,13 +16675,13 @@
         <v>-357.66571718</v>
       </c>
       <c r="E444" t="n">
-        <v>-358.3815133373908</v>
+        <v>-358.3815133373907</v>
       </c>
       <c r="F444" t="n">
         <v>-6623.439207037037</v>
       </c>
       <c r="G444" t="n">
-        <v>-6636.694691433163</v>
+        <v>-6636.694691433162</v>
       </c>
     </row>
     <row r="445">
@@ -16706,7 +16706,7 @@
         <v>-6589.336998148148</v>
       </c>
       <c r="G445" t="n">
-        <v>-6608.831111459884</v>
+        <v>-6608.831111459883</v>
       </c>
     </row>
     <row r="446">
@@ -16750,13 +16750,13 @@
         <v>-358.17030042</v>
       </c>
       <c r="E447" t="n">
-        <v>-359.1073051046033</v>
+        <v>-359.1073051046034</v>
       </c>
       <c r="F447" t="n">
         <v>-6632.783341111111</v>
       </c>
       <c r="G447" t="n">
-        <v>-6650.135279714876</v>
+        <v>-6650.135279714877</v>
       </c>
     </row>
     <row r="448">
@@ -16806,7 +16806,7 @@
         <v>-6639.416213703704</v>
       </c>
       <c r="G449" t="n">
-        <v>-6653.469706568069</v>
+        <v>-6653.469706568068</v>
       </c>
     </row>
     <row r="450">
@@ -16850,13 +16850,13 @@
         <v>-356.35511839</v>
       </c>
       <c r="E451" t="n">
-        <v>-357.1093111814142</v>
+        <v>-357.1093111814141</v>
       </c>
       <c r="F451" t="n">
         <v>-6599.168859074073</v>
       </c>
       <c r="G451" t="n">
-        <v>-6613.13539224841</v>
+        <v>-6613.135392248409</v>
       </c>
     </row>
     <row r="452">
@@ -16875,13 +16875,13 @@
         <v>-353.56151572</v>
       </c>
       <c r="E452" t="n">
-        <v>-353.9617955478425</v>
+        <v>-353.9617955478424</v>
       </c>
       <c r="F452" t="n">
         <v>-6547.435476296296</v>
       </c>
       <c r="G452" t="n">
-        <v>-6554.848065700788</v>
+        <v>-6554.848065700786</v>
       </c>
     </row>
     <row r="453">
@@ -16906,7 +16906,7 @@
         <v>-6604.08564</v>
       </c>
       <c r="G453" t="n">
-        <v>-6529.484034704044</v>
+        <v>-6529.484034704042</v>
       </c>
     </row>
     <row r="454">
@@ -16925,13 +16925,13 @@
         <v>-359.49275875</v>
       </c>
       <c r="E454" t="n">
-        <v>-360.238117170598</v>
+        <v>-360.2381171705979</v>
       </c>
       <c r="F454" t="n">
         <v>-6657.273310185185</v>
       </c>
       <c r="G454" t="n">
-        <v>-6671.076243899963</v>
+        <v>-6671.076243899962</v>
       </c>
     </row>
     <row r="455">
@@ -17025,13 +17025,13 @@
         <v>-359.43143105</v>
       </c>
       <c r="E458" t="n">
-        <v>-360.1972574857535</v>
+        <v>-360.1972574857534</v>
       </c>
       <c r="F458" t="n">
         <v>-6656.137612037037</v>
       </c>
       <c r="G458" t="n">
-        <v>-6670.31958306951</v>
+        <v>-6670.319583069509</v>
       </c>
     </row>
     <row r="459">
@@ -17050,13 +17050,13 @@
         <v>-359.98383992</v>
       </c>
       <c r="E459" t="n">
-        <v>-360.3396301567408</v>
+        <v>-360.3396301567407</v>
       </c>
       <c r="F459" t="n">
         <v>-6666.367405925926</v>
       </c>
       <c r="G459" t="n">
-        <v>-6672.956114013719</v>
+        <v>-6672.956114013717</v>
       </c>
     </row>
     <row r="460">
@@ -17075,13 +17075,13 @@
         <v>-351.23891841</v>
       </c>
       <c r="E460" t="n">
-        <v>-352.6933894318127</v>
+        <v>-352.6933894318126</v>
       </c>
       <c r="F460" t="n">
         <v>-6504.424414999999</v>
       </c>
       <c r="G460" t="n">
-        <v>-6531.359063552087</v>
+        <v>-6531.359063552086</v>
       </c>
     </row>
     <row r="461">
@@ -17106,7 +17106,7 @@
         <v>-6619.057262592592</v>
       </c>
       <c r="G461" t="n">
-        <v>-6633.998534718885</v>
+        <v>-6633.998534718886</v>
       </c>
     </row>
     <row r="462">
@@ -17131,7 +17131,7 @@
         <v>-6658.458543888889</v>
       </c>
       <c r="G462" t="n">
-        <v>-6591.828685636824</v>
+        <v>-6591.828685636822</v>
       </c>
     </row>
     <row r="463">
@@ -17150,13 +17150,13 @@
         <v>-360.56079538</v>
       </c>
       <c r="E463" t="n">
-        <v>-361.3766978888875</v>
+        <v>-361.3766978888874</v>
       </c>
       <c r="F463" t="n">
         <v>-6677.051766296297</v>
       </c>
       <c r="G463" t="n">
-        <v>-6692.161072016435</v>
+        <v>-6692.161072016434</v>
       </c>
     </row>
     <row r="464">
@@ -17175,13 +17175,13 @@
         <v>-355.13965581</v>
       </c>
       <c r="E464" t="n">
-        <v>-356.2008285412736</v>
+        <v>-356.2008285412735</v>
       </c>
       <c r="F464" t="n">
         <v>-6576.660292777779</v>
       </c>
       <c r="G464" t="n">
-        <v>-6596.311639653215</v>
+        <v>-6596.311639653212</v>
       </c>
     </row>
     <row r="465">
@@ -17200,13 +17200,13 @@
         <v>-360.47226347</v>
       </c>
       <c r="E465" t="n">
-        <v>-361.2739261322728</v>
+        <v>-361.2739261322727</v>
       </c>
       <c r="F465" t="n">
         <v>-6675.412286481481</v>
       </c>
       <c r="G465" t="n">
-        <v>-6690.257891338384</v>
+        <v>-6690.257891338383</v>
       </c>
     </row>
     <row r="466">
@@ -17300,13 +17300,13 @@
         <v>-358.7649163</v>
       </c>
       <c r="E469" t="n">
-        <v>-359.8378855340719</v>
+        <v>-359.8378855340718</v>
       </c>
       <c r="F469" t="n">
         <v>-6643.794746296296</v>
       </c>
       <c r="G469" t="n">
-        <v>-6663.664546927257</v>
+        <v>-6663.664546927256</v>
       </c>
     </row>
     <row r="470">
@@ -17350,13 +17350,13 @@
         <v>-358.54395081</v>
       </c>
       <c r="E471" t="n">
-        <v>-359.4423177532112</v>
+        <v>-359.4423177532111</v>
       </c>
       <c r="F471" t="n">
         <v>-6639.702792777778</v>
       </c>
       <c r="G471" t="n">
-        <v>-6656.339217652059</v>
+        <v>-6656.339217652058</v>
       </c>
     </row>
     <row r="472">
@@ -17450,7 +17450,7 @@
         <v>-358.00307596</v>
       </c>
       <c r="E475" t="n">
-        <v>-359.0558797542622</v>
+        <v>-359.0558797542621</v>
       </c>
       <c r="F475" t="n">
         <v>-6629.686591851852</v>
@@ -17550,13 +17550,13 @@
         <v>-365.41040556</v>
       </c>
       <c r="E479" t="n">
-        <v>-366.0737383624661</v>
+        <v>-366.0737383624662</v>
       </c>
       <c r="F479" t="n">
         <v>-6766.859362222223</v>
       </c>
       <c r="G479" t="n">
-        <v>-6779.143303008633</v>
+        <v>-6779.143303008634</v>
       </c>
     </row>
     <row r="480">
@@ -17650,13 +17650,13 @@
         <v>-122.95760041</v>
       </c>
       <c r="E483" t="n">
-        <v>-121.5197433826642</v>
+        <v>-121.5197433826641</v>
       </c>
       <c r="F483" t="n">
         <v>-6830.977800555555</v>
       </c>
       <c r="G483" t="n">
-        <v>-6751.096854592453</v>
+        <v>-6751.096854592452</v>
       </c>
     </row>
     <row r="484">
@@ -17675,13 +17675,13 @@
         <v>-122.71273625</v>
       </c>
       <c r="E484" t="n">
-        <v>-121.3427509527647</v>
+        <v>-121.3427509527646</v>
       </c>
       <c r="F484" t="n">
         <v>-6817.374236111111</v>
       </c>
       <c r="G484" t="n">
-        <v>-6741.26394182026</v>
+        <v>-6741.263941820258</v>
       </c>
     </row>
     <row r="485">
@@ -17775,13 +17775,13 @@
         <v>-364.52638927</v>
       </c>
       <c r="E488" t="n">
-        <v>-365.239260008106</v>
+        <v>-365.2392600081059</v>
       </c>
       <c r="F488" t="n">
         <v>-6750.488690185185</v>
       </c>
       <c r="G488" t="n">
-        <v>-6763.690000150112</v>
+        <v>-6763.69000015011</v>
       </c>
     </row>
     <row r="489">
@@ -17800,13 +17800,13 @@
         <v>-364.00273323</v>
       </c>
       <c r="E489" t="n">
-        <v>-364.8500618842684</v>
+        <v>-364.8500618842685</v>
       </c>
       <c r="F489" t="n">
         <v>-6740.791356111112</v>
       </c>
       <c r="G489" t="n">
-        <v>-6756.482627486453</v>
+        <v>-6756.482627486454</v>
       </c>
     </row>
     <row r="490">
@@ -17825,13 +17825,13 @@
         <v>-124.15130575</v>
       </c>
       <c r="E490" t="n">
-        <v>-122.6099721808754</v>
+        <v>-122.6099721808753</v>
       </c>
       <c r="F490" t="n">
         <v>-6897.294763888889</v>
       </c>
       <c r="G490" t="n">
-        <v>-6811.665121159742</v>
+        <v>-6811.665121159741</v>
       </c>
     </row>
     <row r="491">
@@ -17856,7 +17856,7 @@
         <v>-6727.300664444444</v>
       </c>
       <c r="G491" t="n">
-        <v>-6737.458731172654</v>
+        <v>-6737.458731172653</v>
       </c>
     </row>
     <row r="492">
@@ -17900,13 +17900,13 @@
         <v>-368.84133562</v>
       </c>
       <c r="E493" t="n">
-        <v>-369.5205740506861</v>
+        <v>-369.520574050686</v>
       </c>
       <c r="F493" t="n">
         <v>-6830.395104074073</v>
       </c>
       <c r="G493" t="n">
-        <v>-6842.973593531224</v>
+        <v>-6842.973593531223</v>
       </c>
     </row>
     <row r="494">
@@ -17981,7 +17981,7 @@
         <v>-6736.377025555556</v>
       </c>
       <c r="G496" t="n">
-        <v>-6653.317543687745</v>
+        <v>-6653.317543687746</v>
       </c>
     </row>
     <row r="497">
@@ -18000,13 +18000,13 @@
         <v>-371.38422421</v>
       </c>
       <c r="E497" t="n">
-        <v>-372.1588514112364</v>
+        <v>-372.1588514112363</v>
       </c>
       <c r="F497" t="n">
         <v>-6877.485633518519</v>
       </c>
       <c r="G497" t="n">
-        <v>-6891.830581689562</v>
+        <v>-6891.830581689561</v>
       </c>
     </row>
     <row r="498">
@@ -18031,7 +18031,7 @@
         <v>-6853.988946111112</v>
       </c>
       <c r="G498" t="n">
-        <v>-6778.337077965811</v>
+        <v>-6778.337077965813</v>
       </c>
     </row>
     <row r="499">
@@ -18100,13 +18100,13 @@
         <v>-366.59658401</v>
       </c>
       <c r="E501" t="n">
-        <v>-367.1397412559624</v>
+        <v>-367.1397412559623</v>
       </c>
       <c r="F501" t="n">
         <v>-6788.825629814814</v>
       </c>
       <c r="G501" t="n">
-        <v>-6798.884097332637</v>
+        <v>-6798.884097332636</v>
       </c>
     </row>
     <row r="502">
@@ -18131,7 +18131,7 @@
         <v>-6727.096363888889</v>
       </c>
       <c r="G502" t="n">
-        <v>-6740.569414112019</v>
+        <v>-6740.569414112018</v>
       </c>
     </row>
     <row r="503">
@@ -18225,13 +18225,13 @@
         <v>-363.14993833</v>
       </c>
       <c r="E506" t="n">
-        <v>-363.9616720777663</v>
+        <v>-363.9616720777662</v>
       </c>
       <c r="F506" t="n">
         <v>-6724.998857962963</v>
       </c>
       <c r="G506" t="n">
-        <v>-6740.030964403079</v>
+        <v>-6740.030964403078</v>
       </c>
     </row>
     <row r="507">
@@ -18300,13 +18300,13 @@
         <v>-363.60867981</v>
       </c>
       <c r="E509" t="n">
-        <v>-364.4446975062063</v>
+        <v>-364.4446975062064</v>
       </c>
       <c r="F509" t="n">
         <v>-6733.494070555555</v>
       </c>
       <c r="G509" t="n">
-        <v>-6748.975879744561</v>
+        <v>-6748.975879744562</v>
       </c>
     </row>
     <row r="510">
@@ -18356,7 +18356,7 @@
         <v>-6752.294239444444</v>
       </c>
       <c r="G511" t="n">
-        <v>-6672.256239404509</v>
+        <v>-6672.256239404511</v>
       </c>
     </row>
     <row r="512">
@@ -18381,7 +18381,7 @@
         <v>-6834.640351111111</v>
       </c>
       <c r="G512" t="n">
-        <v>-6760.487651453761</v>
+        <v>-6760.487651453759</v>
       </c>
     </row>
     <row r="513">
@@ -18456,7 +18456,7 @@
         <v>-6718.192337962962</v>
       </c>
       <c r="G515" t="n">
-        <v>-6741.810718219661</v>
+        <v>-6741.810718219659</v>
       </c>
     </row>
     <row r="516">
@@ -18500,13 +18500,13 @@
         <v>-365.81135092</v>
       </c>
       <c r="E517" t="n">
-        <v>-367.1256832815322</v>
+        <v>-367.1256832815321</v>
       </c>
       <c r="F517" t="n">
         <v>-6774.284276296296</v>
       </c>
       <c r="G517" t="n">
-        <v>-6798.623764472818</v>
+        <v>-6798.623764472817</v>
       </c>
     </row>
     <row r="518">
@@ -18550,7 +18550,7 @@
         <v>-362.51402626</v>
       </c>
       <c r="E519" t="n">
-        <v>-362.9521661776368</v>
+        <v>-362.9521661776369</v>
       </c>
       <c r="F519" t="n">
         <v>-6713.222708518518</v>
@@ -18631,7 +18631,7 @@
         <v>-6739.580045</v>
       </c>
       <c r="G522" t="n">
-        <v>-6668.581060911531</v>
+        <v>-6668.581060911529</v>
       </c>
     </row>
     <row r="523">
@@ -18706,7 +18706,7 @@
         <v>-6798.027550740741</v>
       </c>
       <c r="G525" t="n">
-        <v>-6811.502576320649</v>
+        <v>-6811.502576320648</v>
       </c>
     </row>
     <row r="526">
@@ -18831,7 +18831,7 @@
         <v>-6743.417895</v>
       </c>
       <c r="G530" t="n">
-        <v>-6649.908233770844</v>
+        <v>-6649.908233770842</v>
       </c>
     </row>
     <row r="531">
@@ -18850,13 +18850,13 @@
         <v>-123.14762164</v>
       </c>
       <c r="E531" t="n">
-        <v>-121.7330074991294</v>
+        <v>-121.7330074991293</v>
       </c>
       <c r="F531" t="n">
         <v>-6841.534535555556</v>
       </c>
       <c r="G531" t="n">
-        <v>-6762.944861062742</v>
+        <v>-6762.944861062741</v>
       </c>
     </row>
     <row r="532">
@@ -18956,7 +18956,7 @@
         <v>-6736.367434074075</v>
       </c>
       <c r="G535" t="n">
-        <v>-6759.713618439747</v>
+        <v>-6759.713618439746</v>
       </c>
     </row>
     <row r="536">
@@ -19075,7 +19075,7 @@
         <v>-365.60738294</v>
       </c>
       <c r="E540" t="n">
-        <v>-366.6632282043512</v>
+        <v>-366.6632282043511</v>
       </c>
       <c r="F540" t="n">
         <v>-6770.507091481481</v>
@@ -19106,7 +19106,7 @@
         <v>-6796.189723888889</v>
       </c>
       <c r="G541" t="n">
-        <v>-6729.022067268412</v>
+        <v>-6729.022067268411</v>
       </c>
     </row>
     <row r="542">
@@ -19150,13 +19150,13 @@
         <v>-364.25203448</v>
       </c>
       <c r="E543" t="n">
-        <v>-365.1676662051535</v>
+        <v>-365.1676662051534</v>
       </c>
       <c r="F543" t="n">
         <v>-6745.408045925927</v>
       </c>
       <c r="G543" t="n">
-        <v>-6762.364188984324</v>
+        <v>-6762.364188984322</v>
       </c>
     </row>
     <row r="544">
@@ -19200,7 +19200,7 @@
         <v>-364.22201446</v>
       </c>
       <c r="E545" t="n">
-        <v>-364.7548108859074</v>
+        <v>-364.7548108859075</v>
       </c>
       <c r="F545" t="n">
         <v>-6744.852119629631</v>
@@ -19331,7 +19331,7 @@
         <v>-6789.405679444444</v>
       </c>
       <c r="G550" t="n">
-        <v>-6810.985342353977</v>
+        <v>-6810.985342353976</v>
       </c>
     </row>
     <row r="551">
@@ -19350,13 +19350,13 @@
         <v>-363.19283719</v>
       </c>
       <c r="E551" t="n">
-        <v>-363.8991111936677</v>
+        <v>-363.8991111936675</v>
       </c>
       <c r="F551" t="n">
         <v>-6725.793281296296</v>
       </c>
       <c r="G551" t="n">
-        <v>-6738.872429512366</v>
+        <v>-6738.872429512361</v>
       </c>
     </row>
     <row r="552">
@@ -19400,13 +19400,13 @@
         <v>-362.63662437</v>
       </c>
       <c r="E553" t="n">
-        <v>-363.6716377967645</v>
+        <v>-363.6716377967644</v>
       </c>
       <c r="F553" t="n">
         <v>-6715.493043888889</v>
       </c>
       <c r="G553" t="n">
-        <v>-6734.659959199343</v>
+        <v>-6734.65995919934</v>
       </c>
     </row>
     <row r="554">
@@ -19450,13 +19450,13 @@
         <v>-363.30853792</v>
       </c>
       <c r="E555" t="n">
-        <v>-364.0165102310387</v>
+        <v>-364.0165102310386</v>
       </c>
       <c r="F555" t="n">
         <v>-6727.935887407407</v>
       </c>
       <c r="G555" t="n">
-        <v>-6741.046485759975</v>
+        <v>-6741.046485759974</v>
       </c>
     </row>
     <row r="556">
@@ -19506,7 +19506,7 @@
         <v>-6769.881743888889</v>
       </c>
       <c r="G557" t="n">
-        <v>-6692.449617137416</v>
+        <v>-6692.449617137415</v>
       </c>
     </row>
     <row r="558">
@@ -19575,13 +19575,13 @@
         <v>-364.89091838</v>
       </c>
       <c r="E560" t="n">
-        <v>-365.3011891690903</v>
+        <v>-365.3011891690904</v>
       </c>
       <c r="F560" t="n">
         <v>-6757.239229259259</v>
       </c>
       <c r="G560" t="n">
-        <v>-6764.836836464635</v>
+        <v>-6764.836836464637</v>
       </c>
     </row>
     <row r="561">
@@ -19606,7 +19606,7 @@
         <v>-6735.982682222222</v>
       </c>
       <c r="G561" t="n">
-        <v>-6743.040182600321</v>
+        <v>-6743.04018260032</v>
       </c>
     </row>
     <row r="562">
@@ -19631,7 +19631,7 @@
         <v>-6719.568811666667</v>
       </c>
       <c r="G562" t="n">
-        <v>-6736.033729061758</v>
+        <v>-6736.033729061757</v>
       </c>
     </row>
     <row r="563">
@@ -19656,7 +19656,7 @@
         <v>-6729.027347777777</v>
       </c>
       <c r="G563" t="n">
-        <v>-6652.146279750912</v>
+        <v>-6652.14627975091</v>
       </c>
     </row>
     <row r="564">
@@ -19725,13 +19725,13 @@
         <v>-368.42958085</v>
       </c>
       <c r="E566" t="n">
-        <v>-369.5580171095072</v>
+        <v>-369.5580171095073</v>
       </c>
       <c r="F566" t="n">
         <v>-6822.77001574074</v>
       </c>
       <c r="G566" t="n">
-        <v>-6843.666983509394</v>
+        <v>-6843.666983509395</v>
       </c>
     </row>
     <row r="567">
@@ -19756,7 +19756,7 @@
         <v>-6713.306300925927</v>
       </c>
       <c r="G567" t="n">
-        <v>-6727.885040910575</v>
+        <v>-6727.885040910573</v>
       </c>
     </row>
     <row r="568">
@@ -19775,13 +19775,13 @@
         <v>-364.90780386</v>
       </c>
       <c r="E568" t="n">
-        <v>-365.2944560276595</v>
+        <v>-365.2944560276594</v>
       </c>
       <c r="F568" t="n">
         <v>-6757.551923333333</v>
       </c>
       <c r="G568" t="n">
-        <v>-6764.712148660361</v>
+        <v>-6764.712148660359</v>
       </c>
     </row>
     <row r="569">
@@ -19825,13 +19825,13 @@
         <v>-362.59968794</v>
       </c>
       <c r="E570" t="n">
-        <v>-363.0433082981309</v>
+        <v>-363.043308298131</v>
       </c>
       <c r="F570" t="n">
         <v>-6714.809035925927</v>
       </c>
       <c r="G570" t="n">
-        <v>-6723.024227743165</v>
+        <v>-6723.024227743167</v>
       </c>
     </row>
     <row r="571">
@@ -19856,7 +19856,7 @@
         <v>-6742.315502777778</v>
       </c>
       <c r="G571" t="n">
-        <v>-6762.264568640903</v>
+        <v>-6762.264568640904</v>
       </c>
     </row>
     <row r="572">
@@ -19900,13 +19900,13 @@
         <v>-365.5672135</v>
       </c>
       <c r="E573" t="n">
-        <v>-366.0854944698673</v>
+        <v>-366.0854944698674</v>
       </c>
       <c r="F573" t="n">
         <v>-6769.763212962962</v>
       </c>
       <c r="G573" t="n">
-        <v>-6779.361008701246</v>
+        <v>-6779.361008701248</v>
       </c>
     </row>
     <row r="574">
@@ -19950,13 +19950,13 @@
         <v>-363.81438488</v>
       </c>
       <c r="E575" t="n">
-        <v>-364.7571764950091</v>
+        <v>-364.7571764950092</v>
       </c>
       <c r="F575" t="n">
         <v>-6737.303423703703</v>
       </c>
       <c r="G575" t="n">
-        <v>-6754.762527685354</v>
+        <v>-6754.762527685355</v>
       </c>
     </row>
     <row r="576">
@@ -20081,7 +20081,7 @@
         <v>-6775.584307962963</v>
       </c>
       <c r="G580" t="n">
-        <v>-6797.364601063852</v>
+        <v>-6797.364601063851</v>
       </c>
     </row>
     <row r="581">
@@ -20100,13 +20100,13 @@
         <v>-122.74309531</v>
       </c>
       <c r="E581" t="n">
-        <v>-121.2677133373139</v>
+        <v>-121.2677133373138</v>
       </c>
       <c r="F581" t="n">
         <v>-6819.060850555556</v>
       </c>
       <c r="G581" t="n">
-        <v>-6737.095185406326</v>
+        <v>-6737.095185406324</v>
       </c>
     </row>
     <row r="582">
@@ -20125,13 +20125,13 @@
         <v>-366.67947125</v>
       </c>
       <c r="E582" t="n">
-        <v>-367.6956594623825</v>
+        <v>-367.6956594623824</v>
       </c>
       <c r="F582" t="n">
         <v>-6790.360578703704</v>
       </c>
       <c r="G582" t="n">
-        <v>-6809.17887893301</v>
+        <v>-6809.178878933007</v>
       </c>
     </row>
     <row r="583">
@@ -20156,7 +20156,7 @@
         <v>-6732.992421111111</v>
       </c>
       <c r="G583" t="n">
-        <v>-6658.384893977419</v>
+        <v>-6658.384893977418</v>
       </c>
     </row>
     <row r="584">
@@ -20181,7 +20181,7 @@
         <v>-6750.418558333334</v>
       </c>
       <c r="G584" t="n">
-        <v>-6675.535484821917</v>
+        <v>-6675.535484821918</v>
       </c>
     </row>
     <row r="585">
@@ -20200,13 +20200,13 @@
         <v>-365.19369526</v>
       </c>
       <c r="E585" t="n">
-        <v>-365.8985238779037</v>
+        <v>-365.8985238779036</v>
       </c>
       <c r="F585" t="n">
         <v>-6762.846208518518</v>
       </c>
       <c r="G585" t="n">
-        <v>-6775.89859033155</v>
+        <v>-6775.898590331549</v>
       </c>
     </row>
     <row r="586">
@@ -20225,13 +20225,13 @@
         <v>-122.43053405</v>
       </c>
       <c r="E586" t="n">
-        <v>-121.1784669777299</v>
+        <v>-121.1784669777298</v>
       </c>
       <c r="F586" t="n">
         <v>-6801.696336111111</v>
       </c>
       <c r="G586" t="n">
-        <v>-6732.137054318326</v>
+        <v>-6732.137054318325</v>
       </c>
     </row>
     <row r="587">
@@ -20250,13 +20250,13 @@
         <v>-362.71891586</v>
       </c>
       <c r="E587" t="n">
-        <v>-363.5676067672034</v>
+        <v>-363.5676067672033</v>
       </c>
       <c r="F587" t="n">
         <v>-6717.016960370371</v>
       </c>
       <c r="G587" t="n">
-        <v>-6732.733458651915</v>
+        <v>-6732.733458651913</v>
       </c>
     </row>
     <row r="588">
@@ -20350,13 +20350,13 @@
         <v>-368.2403116</v>
       </c>
       <c r="E591" t="n">
-        <v>-369.2717834653616</v>
+        <v>-369.2717834653617</v>
       </c>
       <c r="F591" t="n">
         <v>-6819.265029629629</v>
       </c>
       <c r="G591" t="n">
-        <v>-6838.366360469659</v>
+        <v>-6838.366360469661</v>
       </c>
     </row>
     <row r="592">
@@ -20425,13 +20425,13 @@
         <v>-364.4277787</v>
       </c>
       <c r="E594" t="n">
-        <v>-365.5553283788047</v>
+        <v>-365.5553283788049</v>
       </c>
       <c r="F594" t="n">
         <v>-6748.662568518518</v>
       </c>
       <c r="G594" t="n">
-        <v>-6769.543118126014</v>
+        <v>-6769.543118126016</v>
       </c>
     </row>
     <row r="595">
@@ -20450,13 +20450,13 @@
         <v>-366.76419016</v>
       </c>
       <c r="E595" t="n">
-        <v>-367.4544548596146</v>
+        <v>-367.4544548596147</v>
       </c>
       <c r="F595" t="n">
         <v>-6791.929447407408</v>
       </c>
       <c r="G595" t="n">
-        <v>-6804.7121270299</v>
+        <v>-6804.712127029901</v>
       </c>
     </row>
     <row r="596">
@@ -20481,7 +20481,7 @@
         <v>-6791.145690555556</v>
       </c>
       <c r="G596" t="n">
-        <v>-6715.274668013048</v>
+        <v>-6715.274668013046</v>
       </c>
     </row>
     <row r="597">
@@ -20506,7 +20506,7 @@
         <v>-6758.308479814815</v>
       </c>
       <c r="G597" t="n">
-        <v>-6771.946242292551</v>
+        <v>-6771.946242292552</v>
       </c>
     </row>
     <row r="598">
@@ -20581,7 +20581,7 @@
         <v>-6814.086963888888</v>
       </c>
       <c r="G600" t="n">
-        <v>-6726.56034705145</v>
+        <v>-6726.560347051448</v>
       </c>
     </row>
     <row r="601">
@@ -20600,7 +20600,7 @@
         <v>-366.02658997</v>
       </c>
       <c r="E601" t="n">
-        <v>-366.8516153036847</v>
+        <v>-366.8516153036848</v>
       </c>
       <c r="F601" t="n">
         <v>-6778.27018462963</v>
@@ -20681,7 +20681,7 @@
         <v>-6721.926418333333</v>
       </c>
       <c r="G604" t="n">
-        <v>-6636.527007383369</v>
+        <v>-6636.527007383367</v>
       </c>
     </row>
     <row r="605">
@@ -20781,7 +20781,7 @@
         <v>-6894.844555</v>
       </c>
       <c r="G608" t="n">
-        <v>-6809.873651303963</v>
+        <v>-6809.873651303961</v>
       </c>
     </row>
     <row r="609">
@@ -20800,13 +20800,13 @@
         <v>-366.51489703</v>
       </c>
       <c r="E609" t="n">
-        <v>-367.0380923631224</v>
+        <v>-367.0380923631222</v>
       </c>
       <c r="F609" t="n">
         <v>-6787.312907962963</v>
       </c>
       <c r="G609" t="n">
-        <v>-6797.001710428192</v>
+        <v>-6797.001710428191</v>
       </c>
     </row>
     <row r="610">
@@ -20825,13 +20825,13 @@
         <v>-362.94431163</v>
       </c>
       <c r="E610" t="n">
-        <v>-363.6831387574882</v>
+        <v>-363.6831387574881</v>
       </c>
       <c r="F610" t="n">
         <v>-6721.190956111112</v>
       </c>
       <c r="G610" t="n">
-        <v>-6734.872939953485</v>
+        <v>-6734.872939953483</v>
       </c>
     </row>
     <row r="611">
@@ -20850,13 +20850,13 @@
         <v>-366.69303484</v>
       </c>
       <c r="E611" t="n">
-        <v>-367.7372654698838</v>
+        <v>-367.7372654698837</v>
       </c>
       <c r="F611" t="n">
         <v>-6790.611756296296</v>
       </c>
       <c r="G611" t="n">
-        <v>-6809.949360553403</v>
+        <v>-6809.949360553402</v>
       </c>
     </row>
     <row r="612">
@@ -20875,13 +20875,13 @@
         <v>-365.03073945</v>
       </c>
       <c r="E612" t="n">
-        <v>-366.1881595433132</v>
+        <v>-366.1881595433131</v>
       </c>
       <c r="F612" t="n">
         <v>-6759.828508333333</v>
       </c>
       <c r="G612" t="n">
-        <v>-6781.26221376506</v>
+        <v>-6781.262213765057</v>
       </c>
     </row>
     <row r="613">
@@ -20900,13 +20900,13 @@
         <v>-363.49020779</v>
       </c>
       <c r="E613" t="n">
-        <v>-364.3327108188678</v>
+        <v>-364.3327108188677</v>
       </c>
       <c r="F613" t="n">
         <v>-6731.300144259259</v>
       </c>
       <c r="G613" t="n">
-        <v>-6746.902052201255</v>
+        <v>-6746.902052201254</v>
       </c>
     </row>
     <row r="614">
@@ -20931,7 +20931,7 @@
         <v>-6856.463806111112</v>
       </c>
       <c r="G614" t="n">
-        <v>-6776.836757432497</v>
+        <v>-6776.836757432495</v>
       </c>
     </row>
     <row r="615">
@@ -20981,7 +20981,7 @@
         <v>-6879.104282222223</v>
       </c>
       <c r="G616" t="n">
-        <v>-6893.424865301789</v>
+        <v>-6893.42486530179</v>
       </c>
     </row>
     <row r="617">
@@ -21031,7 +21031,7 @@
         <v>-6813.555061666667</v>
       </c>
       <c r="G618" t="n">
-        <v>-6740.461813646279</v>
+        <v>-6740.46181364628</v>
       </c>
     </row>
     <row r="619">
@@ -21050,7 +21050,7 @@
         <v>-364.829887</v>
       </c>
       <c r="E619" t="n">
-        <v>-365.5392692604572</v>
+        <v>-365.5392692604571</v>
       </c>
       <c r="F619" t="n">
         <v>-6756.109018518518</v>
@@ -21081,7 +21081,7 @@
         <v>-6775.431021111111</v>
       </c>
       <c r="G620" t="n">
-        <v>-6692.769759791478</v>
+        <v>-6692.769759791477</v>
       </c>
     </row>
     <row r="621">
@@ -21231,7 +21231,7 @@
         <v>-6784.519828333334</v>
       </c>
       <c r="G626" t="n">
-        <v>-6704.088992895556</v>
+        <v>-6704.088992895555</v>
       </c>
     </row>
     <row r="627">
@@ -21250,13 +21250,13 @@
         <v>-364.84459906</v>
       </c>
       <c r="E627" t="n">
-        <v>-365.5471655500115</v>
+        <v>-365.5471655500116</v>
       </c>
       <c r="F627" t="n">
         <v>-6756.381464074074</v>
       </c>
       <c r="G627" t="n">
-        <v>-6769.391954629843</v>
+        <v>-6769.391954629845</v>
       </c>
     </row>
     <row r="628">
@@ -21281,7 +21281,7 @@
         <v>-6765.465725185186</v>
       </c>
       <c r="G628" t="n">
-        <v>-6783.659472684341</v>
+        <v>-6783.65947268434</v>
       </c>
     </row>
     <row r="629">
@@ -21306,7 +21306,7 @@
         <v>-6741.594532777778</v>
       </c>
       <c r="G629" t="n">
-        <v>-6669.332180843395</v>
+        <v>-6669.332180843394</v>
       </c>
     </row>
     <row r="630">
@@ -21350,13 +21350,13 @@
         <v>-363.26412556</v>
       </c>
       <c r="E631" t="n">
-        <v>-364.2003209600751</v>
+        <v>-364.2003209600752</v>
       </c>
       <c r="F631" t="n">
         <v>-6727.113436296297</v>
       </c>
       <c r="G631" t="n">
-        <v>-6744.450388149538</v>
+        <v>-6744.45038814954</v>
       </c>
     </row>
     <row r="632">
@@ -21381,7 +21381,7 @@
         <v>-6775.405609444445</v>
       </c>
       <c r="G632" t="n">
-        <v>-6790.812137055738</v>
+        <v>-6790.812137055736</v>
       </c>
     </row>
     <row r="633">
@@ -21400,13 +21400,13 @@
         <v>-363.98082642</v>
       </c>
       <c r="E633" t="n">
-        <v>-364.8238247688588</v>
+        <v>-364.8238247688587</v>
       </c>
       <c r="F633" t="n">
         <v>-6740.385674444446</v>
       </c>
       <c r="G633" t="n">
-        <v>-6755.996754978866</v>
+        <v>-6755.996754978864</v>
       </c>
     </row>
     <row r="634">
@@ -21425,13 +21425,13 @@
         <v>-362.80903906</v>
       </c>
       <c r="E634" t="n">
-        <v>-363.7014921903349</v>
+        <v>-363.7014921903348</v>
       </c>
       <c r="F634" t="n">
         <v>-6718.685908518518</v>
       </c>
       <c r="G634" t="n">
-        <v>-6735.212818339535</v>
+        <v>-6735.212818339533</v>
       </c>
     </row>
     <row r="635">
@@ -21450,13 +21450,13 @@
         <v>-362.82289086</v>
       </c>
       <c r="E635" t="n">
-        <v>-363.2898121440679</v>
+        <v>-363.2898121440678</v>
       </c>
       <c r="F635" t="n">
         <v>-6718.942423333333</v>
       </c>
       <c r="G635" t="n">
-        <v>-6727.589113779035</v>
+        <v>-6727.589113779034</v>
       </c>
     </row>
     <row r="636">
@@ -21481,7 +21481,7 @@
         <v>-6852.466851666667</v>
       </c>
       <c r="G636" t="n">
-        <v>-6774.530497844711</v>
+        <v>-6774.530497844709</v>
       </c>
     </row>
     <row r="637">
@@ -21506,7 +21506,7 @@
         <v>-6773.864571481481</v>
       </c>
       <c r="G637" t="n">
-        <v>-6785.346192852644</v>
+        <v>-6785.346192852645</v>
       </c>
     </row>
     <row r="638">
@@ -21550,13 +21550,13 @@
         <v>-367.84326054</v>
       </c>
       <c r="E639" t="n">
-        <v>-368.6811310456217</v>
+        <v>-368.6811310456218</v>
       </c>
       <c r="F639" t="n">
         <v>-6811.912232222222</v>
       </c>
       <c r="G639" t="n">
-        <v>-6827.428352696697</v>
+        <v>-6827.428352696699</v>
       </c>
     </row>
     <row r="640">
@@ -21581,7 +21581,7 @@
         <v>-6781.325500555556</v>
       </c>
       <c r="G640" t="n">
-        <v>-6710.903149268058</v>
+        <v>-6710.903149268056</v>
       </c>
     </row>
     <row r="641">
@@ -21600,13 +21600,13 @@
         <v>-366.46545692</v>
       </c>
       <c r="E641" t="n">
-        <v>-366.8791140220833</v>
+        <v>-366.8791140220832</v>
       </c>
       <c r="F641" t="n">
         <v>-6786.397350370371</v>
       </c>
       <c r="G641" t="n">
-        <v>-6794.057667075616</v>
+        <v>-6794.057667075615</v>
       </c>
     </row>
     <row r="642">
@@ -21650,13 +21650,13 @@
         <v>-365.87074682</v>
       </c>
       <c r="E643" t="n">
-        <v>-366.6101750043959</v>
+        <v>-366.6101750043958</v>
       </c>
       <c r="F643" t="n">
         <v>-6775.38420037037</v>
       </c>
       <c r="G643" t="n">
-        <v>-6789.07731489622</v>
+        <v>-6789.077314896218</v>
       </c>
     </row>
     <row r="644">
@@ -21675,13 +21675,13 @@
         <v>-122.58911939</v>
       </c>
       <c r="E644" t="n">
-        <v>-121.146093514782</v>
+        <v>-121.1460935147819</v>
       </c>
       <c r="F644" t="n">
         <v>-6810.506632777778</v>
       </c>
       <c r="G644" t="n">
-        <v>-6730.338528598998</v>
+        <v>-6730.338528598997</v>
       </c>
     </row>
     <row r="645">
@@ -21750,13 +21750,13 @@
         <v>-123.3457147</v>
       </c>
       <c r="E647" t="n">
-        <v>-121.7171412926638</v>
+        <v>-121.7171412926637</v>
       </c>
       <c r="F647" t="n">
         <v>-6852.539705555555</v>
       </c>
       <c r="G647" t="n">
-        <v>-6762.063405147987</v>
+        <v>-6762.063405147986</v>
       </c>
     </row>
     <row r="648">
@@ -21825,13 +21825,13 @@
         <v>-366.90124376</v>
       </c>
       <c r="E650" t="n">
-        <v>-367.530311719546</v>
+        <v>-367.5303117195459</v>
       </c>
       <c r="F650" t="n">
         <v>-6794.467477037037</v>
       </c>
       <c r="G650" t="n">
-        <v>-6806.116883695296</v>
+        <v>-6806.116883695295</v>
       </c>
     </row>
     <row r="651">
@@ -21856,7 +21856,7 @@
         <v>-6774.5547</v>
       </c>
       <c r="G651" t="n">
-        <v>-6697.752879757554</v>
+        <v>-6697.752879757555</v>
       </c>
     </row>
     <row r="652">
@@ -21925,13 +21925,13 @@
         <v>-366.30609711</v>
       </c>
       <c r="E654" t="n">
-        <v>-366.9526898798513</v>
+        <v>-366.9526898798512</v>
       </c>
       <c r="F654" t="n">
         <v>-6783.446242777777</v>
       </c>
       <c r="G654" t="n">
-        <v>-6795.420182960209</v>
+        <v>-6795.420182960207</v>
       </c>
     </row>
     <row r="655">
@@ -21975,13 +21975,13 @@
         <v>-123.64023924</v>
       </c>
       <c r="E656" t="n">
-        <v>-122.3737985350304</v>
+        <v>-122.3737985350303</v>
       </c>
       <c r="F656" t="n">
         <v>-6868.90218</v>
       </c>
       <c r="G656" t="n">
-        <v>-6798.544363057244</v>
+        <v>-6798.544363057242</v>
       </c>
     </row>
     <row r="657">
@@ -22106,7 +22106,7 @@
         <v>-6842.611018888889</v>
       </c>
       <c r="G661" t="n">
-        <v>-6762.86442253601</v>
+        <v>-6762.864422536009</v>
       </c>
     </row>
     <row r="662">
@@ -22156,7 +22156,7 @@
         <v>-6724.69363925926</v>
       </c>
       <c r="G663" t="n">
-        <v>-6726.638328926911</v>
+        <v>-6726.638328926912</v>
       </c>
     </row>
     <row r="664">
@@ -22175,13 +22175,13 @@
         <v>-367.05490959</v>
       </c>
       <c r="E664" t="n">
-        <v>-367.7183294348481</v>
+        <v>-367.718329434848</v>
       </c>
       <c r="F664" t="n">
         <v>-6797.313140555555</v>
       </c>
       <c r="G664" t="n">
-        <v>-6809.598693237927</v>
+        <v>-6809.598693237926</v>
       </c>
     </row>
     <row r="665">
@@ -22231,7 +22231,7 @@
         <v>-6718.635703333333</v>
       </c>
       <c r="G666" t="n">
-        <v>-6732.27023105478</v>
+        <v>-6732.270231054779</v>
       </c>
     </row>
     <row r="667">
@@ -22256,7 +22256,7 @@
         <v>-6749.141444814815</v>
       </c>
       <c r="G667" t="n">
-        <v>-6763.773351054616</v>
+        <v>-6763.773351054615</v>
       </c>
     </row>
     <row r="668">
@@ -22275,13 +22275,13 @@
         <v>-363.00285127</v>
       </c>
       <c r="E668" t="n">
-        <v>-363.7394054265064</v>
+        <v>-363.7394054265065</v>
       </c>
       <c r="F668" t="n">
         <v>-6722.275023518519</v>
       </c>
       <c r="G668" t="n">
-        <v>-6735.914915305674</v>
+        <v>-6735.914915305675</v>
       </c>
     </row>
     <row r="669">
@@ -22375,13 +22375,13 @@
         <v>-362.87904666</v>
       </c>
       <c r="E672" t="n">
-        <v>-363.7544279586429</v>
+        <v>-363.7544279586428</v>
       </c>
       <c r="F672" t="n">
         <v>-6719.982345555555</v>
       </c>
       <c r="G672" t="n">
-        <v>-6736.193110345238</v>
+        <v>-6736.193110345236</v>
       </c>
     </row>
     <row r="673">
@@ -22475,13 +22475,13 @@
         <v>-366.33062195</v>
       </c>
       <c r="E676" t="n">
-        <v>-367.2729568049913</v>
+        <v>-367.2729568049914</v>
       </c>
       <c r="F676" t="n">
         <v>-6783.900406481482</v>
       </c>
       <c r="G676" t="n">
-        <v>-6801.351051944284</v>
+        <v>-6801.351051944285</v>
       </c>
     </row>
     <row r="677">
@@ -22531,7 +22531,7 @@
         <v>-6857.913395</v>
       </c>
       <c r="G678" t="n">
-        <v>-6779.308821895763</v>
+        <v>-6779.308821895761</v>
       </c>
     </row>
     <row r="679">
@@ -22581,7 +22581,7 @@
         <v>-6836.987929444444</v>
       </c>
       <c r="G680" t="n">
-        <v>-6755.315956814034</v>
+        <v>-6755.315956814032</v>
       </c>
     </row>
     <row r="681">
@@ -22600,13 +22600,13 @@
         <v>-363.73530937</v>
       </c>
       <c r="E681" t="n">
-        <v>-364.852882448056</v>
+        <v>-364.8528824480559</v>
       </c>
       <c r="F681" t="n">
         <v>-6735.839062407407</v>
       </c>
       <c r="G681" t="n">
-        <v>-6756.534860149185</v>
+        <v>-6756.534860149183</v>
       </c>
     </row>
     <row r="682">
@@ -22625,13 +22625,13 @@
         <v>-365.12523974</v>
       </c>
       <c r="E682" t="n">
-        <v>-365.7566348199604</v>
+        <v>-365.7566348199605</v>
       </c>
       <c r="F682" t="n">
         <v>-6761.578513703704</v>
       </c>
       <c r="G682" t="n">
-        <v>-6773.271015184452</v>
+        <v>-6773.271015184454</v>
       </c>
     </row>
     <row r="683">
@@ -22756,7 +22756,7 @@
         <v>-6721.880250925926</v>
       </c>
       <c r="G687" t="n">
-        <v>-6746.678143148195</v>
+        <v>-6746.678143148194</v>
       </c>
     </row>
     <row r="688">
@@ -22781,7 +22781,7 @@
         <v>-6771.925027777778</v>
       </c>
       <c r="G688" t="n">
-        <v>-6687.026436261579</v>
+        <v>-6687.026436261577</v>
       </c>
     </row>
     <row r="689">
@@ -22800,13 +22800,13 @@
         <v>-363.26435833</v>
       </c>
       <c r="E689" t="n">
-        <v>-363.9398590356493</v>
+        <v>-363.9398590356492</v>
       </c>
       <c r="F689" t="n">
         <v>-6727.117746851852</v>
       </c>
       <c r="G689" t="n">
-        <v>-6739.627019178691</v>
+        <v>-6739.627019178689</v>
       </c>
     </row>
     <row r="690">
@@ -22831,7 +22831,7 @@
         <v>-6835.931640555556</v>
       </c>
       <c r="G690" t="n">
-        <v>-6763.500910621735</v>
+        <v>-6763.500910621733</v>
       </c>
     </row>
     <row r="691">
@@ -22856,7 +22856,7 @@
         <v>-6782.398228703703</v>
       </c>
       <c r="G691" t="n">
-        <v>-6798.334618478144</v>
+        <v>-6798.334618478145</v>
       </c>
     </row>
     <row r="692">
@@ -22931,7 +22931,7 @@
         <v>-6831.255479444445</v>
       </c>
       <c r="G694" t="n">
-        <v>-6749.441645050739</v>
+        <v>-6749.441645050738</v>
       </c>
     </row>
     <row r="695">
@@ -22981,7 +22981,7 @@
         <v>-6720.41170537037</v>
       </c>
       <c r="G696" t="n">
-        <v>-6735.678536333547</v>
+        <v>-6735.678536333546</v>
       </c>
     </row>
     <row r="697">
@@ -23006,7 +23006,7 @@
         <v>-6809.033360925927</v>
       </c>
       <c r="G697" t="n">
-        <v>-6826.014487646239</v>
+        <v>-6826.01448764624</v>
       </c>
     </row>
     <row r="698">
@@ -23056,7 +23056,7 @@
         <v>-6739.444536481482</v>
       </c>
       <c r="G699" t="n">
-        <v>-6762.789251628127</v>
+        <v>-6762.789251628126</v>
       </c>
     </row>
     <row r="700">
@@ -23075,13 +23075,13 @@
         <v>-364.16846816</v>
       </c>
       <c r="E700" t="n">
-        <v>-365.2140611909448</v>
+        <v>-365.2140611909449</v>
       </c>
       <c r="F700" t="n">
         <v>-6743.860521481482</v>
       </c>
       <c r="G700" t="n">
-        <v>-6763.223355387868</v>
+        <v>-6763.223355387869</v>
       </c>
     </row>
     <row r="701">
@@ -23175,13 +23175,13 @@
         <v>-369.52145964</v>
       </c>
       <c r="E704" t="n">
-        <v>-370.3523227963759</v>
+        <v>-370.352322796376</v>
       </c>
       <c r="F704" t="n">
         <v>-6842.989993333334</v>
       </c>
       <c r="G704" t="n">
-        <v>-6858.376348081035</v>
+        <v>-6858.376348081037</v>
       </c>
     </row>
     <row r="705">
@@ -23206,7 +23206,7 @@
         <v>-6762.819622777778</v>
       </c>
       <c r="G705" t="n">
-        <v>-6677.784467595578</v>
+        <v>-6677.784467595577</v>
       </c>
     </row>
     <row r="706">
@@ -23231,7 +23231,7 @@
         <v>-6779.341541481482</v>
       </c>
       <c r="G706" t="n">
-        <v>-6785.863085741887</v>
+        <v>-6785.863085741888</v>
       </c>
     </row>
     <row r="707">
@@ -23406,7 +23406,7 @@
         <v>-6813.912629444445</v>
       </c>
       <c r="G713" t="n">
-        <v>-6739.867297661611</v>
+        <v>-6739.867297661609</v>
       </c>
     </row>
     <row r="714">
@@ -23481,7 +23481,7 @@
         <v>-6859.283624444444</v>
       </c>
       <c r="G716" t="n">
-        <v>-6789.366673495068</v>
+        <v>-6789.366673495067</v>
       </c>
     </row>
     <row r="717">
@@ -23500,13 +23500,13 @@
         <v>-367.9826885</v>
       </c>
       <c r="E717" t="n">
-        <v>-369.1170379485686</v>
+        <v>-369.1170379485687</v>
       </c>
       <c r="F717" t="n">
         <v>-6814.494231481482</v>
       </c>
       <c r="G717" t="n">
-        <v>-6835.500702751271</v>
+        <v>-6835.500702751273</v>
       </c>
     </row>
     <row r="718">
@@ -23631,7 +23631,7 @@
         <v>-7201.673554375</v>
       </c>
       <c r="G722" t="n">
-        <v>-7196.393827678215</v>
+        <v>-7196.393827678214</v>
       </c>
     </row>
     <row r="723">
@@ -23650,13 +23650,13 @@
         <v>-117.06996556</v>
       </c>
       <c r="E723" t="n">
-        <v>-116.9845093529856</v>
+        <v>-116.9845093529857</v>
       </c>
       <c r="F723" t="n">
         <v>-7316.8728475</v>
       </c>
       <c r="G723" t="n">
-        <v>-7311.531834561602</v>
+        <v>-7311.531834561603</v>
       </c>
     </row>
     <row r="724">
@@ -23675,13 +23675,13 @@
         <v>-119.31214876</v>
       </c>
       <c r="E724" t="n">
-        <v>-119.2812532701175</v>
+        <v>-119.2812532701174</v>
       </c>
       <c r="F724" t="n">
         <v>-7457.0092975</v>
       </c>
       <c r="G724" t="n">
-        <v>-7455.078329382342</v>
+        <v>-7455.078329382341</v>
       </c>
     </row>
     <row r="725">
@@ -23706,7 +23706,7 @@
         <v>-7470.899701875</v>
       </c>
       <c r="G725" t="n">
-        <v>-7467.530332105025</v>
+        <v>-7467.530332105026</v>
       </c>
     </row>
     <row r="726">
@@ -23731,7 +23731,7 @@
         <v>-7377.93681125</v>
       </c>
       <c r="G726" t="n">
-        <v>-7372.243133801177</v>
+        <v>-7372.243133801174</v>
       </c>
     </row>
     <row r="727">
@@ -23781,7 +23781,7 @@
         <v>-7404.959011875</v>
       </c>
       <c r="G728" t="n">
-        <v>-7402.715868696351</v>
+        <v>-7402.715868696348</v>
       </c>
     </row>
     <row r="729">
@@ -23856,7 +23856,7 @@
         <v>-7499.621015625</v>
       </c>
       <c r="G731" t="n">
-        <v>-7497.524507388431</v>
+        <v>-7497.52450738843</v>
       </c>
     </row>
     <row r="732">
@@ -23875,13 +23875,13 @@
         <v>-118.95580167</v>
       </c>
       <c r="E732" t="n">
-        <v>-118.854979731882</v>
+        <v>-118.8549797318819</v>
       </c>
       <c r="F732" t="n">
         <v>-7434.737604375</v>
       </c>
       <c r="G732" t="n">
-        <v>-7428.436233242623</v>
+        <v>-7428.436233242621</v>
       </c>
     </row>
     <row r="733">
@@ -23956,7 +23956,7 @@
         <v>-7187.7306625</v>
       </c>
       <c r="G735" t="n">
-        <v>-7184.978633691615</v>
+        <v>-7184.978633691614</v>
       </c>
     </row>
     <row r="736">
@@ -23981,7 +23981,7 @@
         <v>-7228.727198125</v>
       </c>
       <c r="G736" t="n">
-        <v>-7229.453297154465</v>
+        <v>-7229.453297154464</v>
       </c>
     </row>
     <row r="737">
@@ -24031,7 +24031,7 @@
         <v>-7337.577519375001</v>
       </c>
       <c r="G738" t="n">
-        <v>-7331.621308644045</v>
+        <v>-7331.621308644043</v>
       </c>
     </row>
     <row r="739">
@@ -24081,7 +24081,7 @@
         <v>-7475.740811875</v>
       </c>
       <c r="G740" t="n">
-        <v>-7476.978677210112</v>
+        <v>-7476.978677210111</v>
       </c>
     </row>
     <row r="741">
@@ -24131,7 +24131,7 @@
         <v>-7535.39257375</v>
       </c>
       <c r="G742" t="n">
-        <v>-7532.285786780466</v>
+        <v>-7532.285786780465</v>
       </c>
     </row>
     <row r="743">
@@ -24200,13 +24200,13 @@
         <v>-130.57714122</v>
       </c>
       <c r="E745" t="n">
-        <v>-130.873282663553</v>
+        <v>-130.8732826635529</v>
       </c>
       <c r="F745" t="n">
         <v>-8161.071326249999</v>
       </c>
       <c r="G745" t="n">
-        <v>-8179.58016647206</v>
+        <v>-8179.580166472059</v>
       </c>
     </row>
     <row r="746">
@@ -24231,7 +24231,7 @@
         <v>-7999.592494375001</v>
       </c>
       <c r="G746" t="n">
-        <v>-8020.613022209672</v>
+        <v>-8020.61302220967</v>
       </c>
     </row>
     <row r="747">
@@ -24281,7 +24281,7 @@
         <v>-8242.7587</v>
       </c>
       <c r="G748" t="n">
-        <v>-8270.99568809729</v>
+        <v>-8270.995688097286</v>
       </c>
     </row>
     <row r="749">
@@ -24331,7 +24331,7 @@
         <v>-7999.141105625</v>
       </c>
       <c r="G750" t="n">
-        <v>-8020.122439062082</v>
+        <v>-8020.12243906208</v>
       </c>
     </row>
     <row r="751">
@@ -24356,7 +24356,7 @@
         <v>-8143.484071250001</v>
       </c>
       <c r="G751" t="n">
-        <v>-8161.477075636994</v>
+        <v>-8161.477075636992</v>
       </c>
     </row>
     <row r="752">
@@ -24381,7 +24381,7 @@
         <v>-8191.05556125</v>
       </c>
       <c r="G752" t="n">
-        <v>-8210.660515130461</v>
+        <v>-8210.660515130459</v>
       </c>
     </row>
     <row r="753">
@@ -24550,13 +24550,13 @@
         <v>-131.87395602</v>
       </c>
       <c r="E759" t="n">
-        <v>-132.2772596777377</v>
+        <v>-132.2772596777376</v>
       </c>
       <c r="F759" t="n">
         <v>-8242.122251250001</v>
       </c>
       <c r="G759" t="n">
-        <v>-8267.328729858606</v>
+        <v>-8267.328729858604</v>
       </c>
     </row>
     <row r="760">
@@ -24706,7 +24706,7 @@
         <v>-8052.277868124999</v>
       </c>
       <c r="G765" t="n">
-        <v>-8073.347124622851</v>
+        <v>-8073.347124622849</v>
       </c>
     </row>
     <row r="766">
@@ -24781,7 +24781,7 @@
         <v>-7984.5798975</v>
       </c>
       <c r="G768" t="n">
-        <v>-8006.074370082528</v>
+        <v>-8006.074370082526</v>
       </c>
     </row>
     <row r="769">
@@ -24806,7 +24806,7 @@
         <v>-7996.033085625</v>
       </c>
       <c r="G769" t="n">
-        <v>-8022.444610846243</v>
+        <v>-8022.444610846242</v>
       </c>
     </row>
     <row r="770">
@@ -24831,7 +24831,7 @@
         <v>-8160.505259375001</v>
       </c>
       <c r="G770" t="n">
-        <v>-8178.270161517961</v>
+        <v>-8178.270161517959</v>
       </c>
     </row>
     <row r="771">
@@ -24956,7 +24956,7 @@
         <v>-7983.566850625</v>
       </c>
       <c r="G775" t="n">
-        <v>-8008.158748890926</v>
+        <v>-8008.158748890924</v>
       </c>
     </row>
     <row r="776">
@@ -25031,7 +25031,7 @@
         <v>-7999.630059375</v>
       </c>
       <c r="G778" t="n">
-        <v>-8020.652416095876</v>
+        <v>-8020.652416095874</v>
       </c>
     </row>
     <row r="779">
@@ -25125,13 +25125,13 @@
         <v>-129.96106203</v>
       </c>
       <c r="E782" t="n">
-        <v>-130.257689046262</v>
+        <v>-130.2576890462619</v>
       </c>
       <c r="F782" t="n">
         <v>-8122.566376875</v>
       </c>
       <c r="G782" t="n">
-        <v>-8141.105565391373</v>
+        <v>-8141.105565391371</v>
       </c>
     </row>
     <row r="783">
@@ -25175,13 +25175,13 @@
         <v>-125.38173989</v>
       </c>
       <c r="E784" t="n">
-        <v>-125.3152029344407</v>
+        <v>-125.3152029344408</v>
       </c>
       <c r="F784" t="n">
         <v>-7836.358743125001</v>
       </c>
       <c r="G784" t="n">
-        <v>-7832.200183402547</v>
+        <v>-7832.200183402548</v>
       </c>
     </row>
     <row r="785">
@@ -25231,7 +25231,7 @@
         <v>-7603.610691875</v>
       </c>
       <c r="G786" t="n">
-        <v>-7596.611112741231</v>
+        <v>-7596.611112741232</v>
       </c>
     </row>
     <row r="787">
@@ -25250,13 +25250,13 @@
         <v>-123.07091219</v>
       </c>
       <c r="E787" t="n">
-        <v>-123.0087817351191</v>
+        <v>-123.008781735119</v>
       </c>
       <c r="F787" t="n">
         <v>-7691.932011875</v>
       </c>
       <c r="G787" t="n">
-        <v>-7688.048858444941</v>
+        <v>-7688.04885844494</v>
       </c>
     </row>
     <row r="788">
@@ -25331,7 +25331,7 @@
         <v>-7751.387919375001</v>
       </c>
       <c r="G790" t="n">
-        <v>-7748.388005297167</v>
+        <v>-7748.388005297169</v>
       </c>
     </row>
     <row r="791">
@@ -25400,13 +25400,13 @@
         <v>-123.02080942</v>
       </c>
       <c r="E793" t="n">
-        <v>-122.9907723691065</v>
+        <v>-122.9907723691064</v>
       </c>
       <c r="F793" t="n">
         <v>-7688.80058875</v>
       </c>
       <c r="G793" t="n">
-        <v>-7686.923273069153</v>
+        <v>-7686.923273069152</v>
       </c>
     </row>
     <row r="794">
@@ -25450,13 +25450,13 @@
         <v>-126.66369414</v>
       </c>
       <c r="E795" t="n">
-        <v>-126.8001977720155</v>
+        <v>-126.8001977720154</v>
       </c>
       <c r="F795" t="n">
         <v>-7916.48088375</v>
       </c>
       <c r="G795" t="n">
-        <v>-7925.012360750967</v>
+        <v>-7925.012360750965</v>
       </c>
     </row>
     <row r="796">
@@ -25506,7 +25506,7 @@
         <v>-7766.1590225</v>
       </c>
       <c r="G797" t="n">
-        <v>-7763.19901133357</v>
+        <v>-7763.199011333571</v>
       </c>
     </row>
     <row r="798">
@@ -25556,7 +25556,7 @@
         <v>-7670.129229375</v>
       </c>
       <c r="G799" t="n">
-        <v>-7665.372863403793</v>
+        <v>-7665.372863403791</v>
       </c>
     </row>
     <row r="800">
@@ -25575,13 +25575,13 @@
         <v>-122.86258983</v>
       </c>
       <c r="E800" t="n">
-        <v>-122.7840567367885</v>
+        <v>-122.7840567367884</v>
       </c>
       <c r="F800" t="n">
         <v>-7678.911864375001</v>
       </c>
       <c r="G800" t="n">
-        <v>-7674.003546049279</v>
+        <v>-7674.003546049278</v>
       </c>
     </row>
     <row r="801">
@@ -25625,13 +25625,13 @@
         <v>-113.30642452</v>
       </c>
       <c r="E802" t="n">
-        <v>-111.9632051615018</v>
+        <v>-111.9632051615017</v>
       </c>
       <c r="F802" t="n">
         <v>-6294.801362222222</v>
       </c>
       <c r="G802" t="n">
-        <v>-6220.178064527876</v>
+        <v>-6220.178064527874</v>
       </c>
     </row>
   </sheetData>
@@ -25680,13 +25680,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.07632031808872</v>
+        <v>40.07632031808894</v>
       </c>
       <c r="D2" t="n">
-        <v>29.16391050784887</v>
+        <v>29.16391050784891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9888814911574271</v>
+        <v>0.988881491157427</v>
       </c>
     </row>
     <row r="3">
@@ -25699,10 +25699,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.64649478938326</v>
+        <v>34.64649478938334</v>
       </c>
       <c r="D3" t="n">
-        <v>24.74762614702206</v>
+        <v>24.74762614702191</v>
       </c>
       <c r="E3" t="n">
         <v>0.9911007410187419</v>
@@ -25805,10 +25805,10 @@
         <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>77.89785939395617</v>
+        <v>77.89785939395669</v>
       </c>
       <c r="F2" t="n">
-        <v>77.54174838537737</v>
+        <v>77.54174838537791</v>
       </c>
     </row>
     <row r="3">
@@ -25829,10 +25829,10 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>4.304412905780117</v>
+        <v>4.304412905780093</v>
       </c>
       <c r="F3" t="n">
-        <v>3.715846632003831</v>
+        <v>3.715846632004059</v>
       </c>
     </row>
     <row r="4">
@@ -25853,10 +25853,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>21.58326814941468</v>
+        <v>21.58326814941449</v>
       </c>
       <c r="F4" t="n">
-        <v>21.49154902146355</v>
+        <v>21.49154902146339</v>
       </c>
     </row>
     <row r="5">
@@ -25877,10 +25877,10 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>15.27505120702909</v>
+        <v>15.27505120702897</v>
       </c>
       <c r="F5" t="n">
-        <v>14.63486182167602</v>
+        <v>14.63486182167587</v>
       </c>
     </row>
     <row r="6">
@@ -25901,10 +25901,10 @@
         <v>132</v>
       </c>
       <c r="E6" t="n">
-        <v>78.17242323889523</v>
+        <v>78.17242323889575</v>
       </c>
       <c r="F6" t="n">
-        <v>77.90531719283051</v>
+        <v>77.90531719283101</v>
       </c>
     </row>
     <row r="7">
@@ -25925,10 +25925,10 @@
         <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>4.162902304319986</v>
+        <v>4.162902304320284</v>
       </c>
       <c r="F7" t="n">
-        <v>3.770029618972587</v>
+        <v>3.770029618972843</v>
       </c>
     </row>
     <row r="8">
@@ -25949,10 +25949,10 @@
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>20.38948511724081</v>
+        <v>20.38948511724008</v>
       </c>
       <c r="F8" t="n">
-        <v>19.72130103971513</v>
+        <v>19.72130103971442</v>
       </c>
     </row>
     <row r="9">
@@ -25973,10 +25973,10 @@
         <v>590</v>
       </c>
       <c r="E9" t="n">
-        <v>15.26913871492006</v>
+        <v>15.26913871491977</v>
       </c>
       <c r="F9" t="n">
-        <v>14.58214148742798</v>
+        <v>14.5821414874277</v>
       </c>
     </row>
   </sheetData>
